--- a/docs/tarifs/Grille-tarifaire-Stackup.xlsx
+++ b/docs/tarifs/Grille-tarifaire-Stackup.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="838">
   <si>
     <t xml:space="preserve">Grille tarifaire Stackup Agency — version de travail du 14/10/2026</t>
   </si>
@@ -861,6 +861,36 @@
     <t xml:space="preserve">O30</t>
   </si>
   <si>
+    <t xml:space="preserve">Devis et factures automatiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facturation électronique conforme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commande vocale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatisations sur mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant IA métier sur mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O35</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sous-total modules</t>
   </si>
   <si>
@@ -933,93 +963,78 @@
     <t xml:space="preserve">8. AVANT LA SIGNATURE ET CONDITIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Démo payée (15 €)</t>
+    <t xml:space="preserve">Rendez-vous supplémentaires (heures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilomètres au-delà de 40 km (aller-retour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Délai accéléré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remise commerciale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au feeling, en pourcentage (ex. 5 %).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RÉSULTAT — CRÉATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total brut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total après coefficient, urgence et remise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL CRÉATION (prix du devis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompte à la signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fourchette à afficher : bas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fourchette à afficher : haut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiement en 4 fois possible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPS ET RENTABILITÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temps estimé (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux horaire effectif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À comparer au taux cible des Paramètres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Délai indicatif : minimum (semaines)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Délai indicatif : maximum (semaines)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. ABONNEMENT MENSUEL (facultatif)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abonnement souhaité</t>
   </si>
   <si>
     <t xml:space="preserve">Oui</t>
   </si>
   <si>
-    <t xml:space="preserve">Non si tu l'as offerte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visio payée (30 €)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rendez-vous supplémentaires (heures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilomètres au-delà de 40 km (aller-retour)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Délai accéléré</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remise commerciale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Au feeling, en pourcentage (ex. 5 %).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RÉSULTAT — CRÉATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total brut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total après coefficient, urgence et remise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL CRÉATION (prix du devis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déduction démo / visio déjà payées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reste à payer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acompte à la signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fourchette à afficher : bas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fourchette à afficher : haut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paiement en 4 fois possible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMPS ET RENTABILITÉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temps estimé (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taux horaire effectif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À comparer au taux cible des Paramètres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Délai indicatif : minimum (semaines)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Délai indicatif : maximum (semaines)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. ABONNEMENT MENSUEL (facultatif)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abonnement souhaité</t>
-  </si>
-  <si>
     <t xml:space="preserve">Publications courtes par mois</t>
   </si>
   <si>
@@ -1233,7 +1248,7 @@
     <t xml:space="preserve">On réalise la page d'accueil de votre site, à votre image, pour que vous puissiez juger sur pièce avant de décider.</t>
   </si>
   <si>
-    <t xml:space="preserve">15 € ; offerte à ta discrétion. Déduite du devis si le client signe. Plafond conseillé : ~6 h de travail.</t>
+    <t xml:space="preserve">15 € ; offerte à ta discrétion. NON déduite du devis (ne pas le préciser au client). Plafond conseillé : ~6 h de travail.</t>
   </si>
   <si>
     <t xml:space="preserve">P03</t>
@@ -1245,7 +1260,7 @@
     <t xml:space="preserve">On vous présente la démo, on échange sur vos besoins, on vous conseille et on ajuste le projet et le prix ensemble.</t>
   </si>
   <si>
-    <t xml:space="preserve">30 € ; déduite du devis si le client signe.</t>
+    <t xml:space="preserve">30 € ; NON déduite du devis (ne pas le préciser au client).</t>
   </si>
   <si>
     <t xml:space="preserve">PENDANT LA CRÉATION (inclus dans le devis)</t>
@@ -1944,6 +1959,39 @@
     <t xml:space="preserve">Via un service spécialisé (coût d'usage refacturé).</t>
   </si>
   <si>
+    <t xml:space="preserve">MODULES — AUTOMATISATION ET INTELLIGENCE ARTIFICIELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le devis se remplit à partir de vos prix habituels ; la facture part toute seule quand le chantier est terminé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppose O02 et O03.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envoi et réception des factures électroniques via une plateforme agréée, comme l'impose la réforme française.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendrier de la réforme et plateforme à vérifier au devis ; abonnement de la plateforme refacturé au réel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous dictez (« j'ai vu M. Martin, 3 fenêtres PVC… ») et l'outil crée le devis, le rendez-vous ou la tâche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ coût d'usage de la reconnaissance vocale / IA refacturé au réel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relances, rappels, tâches répétitives qui se font toutes seules (ex. relance de devis à J+7, rappel de rendez-vous la veille).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">par scénario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une IA conçue pour votre activité, qui connaît vos prix, vos clients et vos habitudes, et vous conseille sans qu'on lui demande.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ coût d'usage refacturé au réel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Les données circulent entre le site et l'outil (réservations, commandes, demandes).</t>
   </si>
   <si>
@@ -2391,7 +2439,7 @@
     <t xml:space="preserve">Démo et visio</t>
   </si>
   <si>
-    <t xml:space="preserve">Démo 15 € et visio 30 € déduites du devis si le client signe. La démo reste ta propriété si le client ne signe pas.</t>
+    <t xml:space="preserve">Démo 15 € et visio 30 € facturées à part, non remboursables. La démo reste ta propriété si le client ne signe pas.</t>
   </si>
   <si>
     <t xml:space="preserve">Nouveau</t>
@@ -3339,12 +3387,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3355,27 +3403,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -3387,13 +3435,13 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>90</v>
@@ -3406,19 +3454,19 @@
         <v>45</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="D7" s="38" t="n">
         <v>40</v>
@@ -3431,21 +3479,21 @@
         <v>40</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>180</v>
@@ -3458,19 +3506,19 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>120</v>
@@ -3483,19 +3531,19 @@
         <v>48</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>725</v>
+        <v>741</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>150</v>
@@ -3508,16 +3556,16 @@
         <v>50</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>726</v>
+        <v>742</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="38" t="n">
@@ -3531,19 +3579,19 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>728</v>
+        <v>744</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="D12" s="38" t="n">
         <v>60</v>
@@ -3556,19 +3604,19 @@
         <v>48</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>731</v>
+        <v>747</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
       <c r="D13" s="38" t="n">
         <v>0</v>
@@ -3581,13 +3629,13 @@
         <v/>
       </c>
       <c r="G13" s="31" t="s">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="H13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3599,10 +3647,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="38" t="n">
@@ -3616,19 +3664,19 @@
         <v>40</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H15" s="31"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>738</v>
+        <v>754</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>90</v>
@@ -3641,21 +3689,21 @@
         <v>60</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="D17" s="34" t="n">
         <v>0.3</v>
@@ -3668,18 +3716,18 @@
         <v/>
       </c>
       <c r="G17" s="31" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="C18" s="31"/>
       <c r="D18" s="34" t="n">
@@ -3693,18 +3741,18 @@
         <v/>
       </c>
       <c r="G18" s="31" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="38" t="n">
@@ -3718,18 +3766,18 @@
         <v/>
       </c>
       <c r="G19" s="31" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="38" t="n">
@@ -3743,19 +3791,19 @@
         <v/>
       </c>
       <c r="G20" s="31" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H20" s="31"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>120</v>
@@ -3768,7 +3816,7 @@
         <v>48</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>758</v>
+        <v>774</v>
       </c>
       <c r="H21" s="31"/>
     </row>
@@ -3799,276 +3847,276 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>789</v>
+        <v>805</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>797</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>798</v>
+        <v>814</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>799</v>
+        <v>815</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>803</v>
+        <v>819</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
       <c r="B21" s="31" t="s">
+        <v>822</v>
+      </c>
+      <c r="C21" s="31" t="s">
         <v>806</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>807</v>
+        <v>823</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>809</v>
+        <v>825</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>812</v>
+        <v>828</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>813</v>
+        <v>829</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>814</v>
+        <v>830</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
@@ -4088,7 +4136,7 @@
     <tabColor rgb="FF0D2C4C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -5798,15 +5846,15 @@
         <v>207</v>
       </c>
       <c r="C111" s="17" t="n">
-        <f aca="false">INDEX('Outil de gestion'!$B$55:$B$58,MATCH(C110,'Outil de gestion'!$A$55:$A$58,1))</f>
+        <f aca="false">INDEX('Outil de gestion'!$B$61:$B$64,MATCH(C110,'Outil de gestion'!$A$61:$A$64,1))</f>
         <v>0</v>
       </c>
       <c r="D111" s="17" t="n">
-        <f aca="false">INDEX('Outil de gestion'!$B$55:$B$58,MATCH(D110,'Outil de gestion'!$A$55:$A$58,1))</f>
+        <f aca="false">INDEX('Outil de gestion'!$B$61:$B$64,MATCH(D110,'Outil de gestion'!$A$61:$A$64,1))</f>
         <v>0</v>
       </c>
       <c r="E111" s="17" t="n">
-        <f aca="false">INDEX('Outil de gestion'!$B$55:$B$58,MATCH(E110,'Outil de gestion'!$A$55:$A$58,1))</f>
+        <f aca="false">INDEX('Outil de gestion'!$B$61:$B$64,MATCH(E110,'Outil de gestion'!$A$61:$A$64,1))</f>
         <v>0</v>
       </c>
       <c r="F111" s="2"/>
@@ -6362,158 +6410,158 @@
       <c r="F143" s="2"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="19" t="s">
+      <c r="A144" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C144" s="20" t="n">
-        <f aca="false">C114*'Outil de gestion'!$D$8+C115*'Outil de gestion'!$D$9+C116*'Outil de gestion'!$D$10+C117*'Outil de gestion'!$D$11+C118*'Outil de gestion'!$D$12+C119*'Outil de gestion'!$D$13+C120*'Outil de gestion'!$D$15+C121*'Outil de gestion'!$D$16+C122*'Outil de gestion'!$D$17+C123*'Outil de gestion'!$D$18+C124*'Outil de gestion'!$D$19+C125*'Outil de gestion'!$D$20+C126*'Outil de gestion'!$D$21+C127*'Outil de gestion'!$D$22+C128*'Outil de gestion'!$D$24+C129*'Outil de gestion'!$D$25+C130*'Outil de gestion'!$D$26+C131*'Outil de gestion'!$D$27+C132*'Outil de gestion'!$D$28+C133*'Outil de gestion'!$D$29+C134*'Outil de gestion'!$D$31+C135*'Outil de gestion'!$D$32+C136*'Outil de gestion'!$D$33+C137*'Outil de gestion'!$D$34+C138*'Outil de gestion'!$D$35+C139*'Outil de gestion'!$D$37+C140*'Outil de gestion'!$D$38+C141*'Outil de gestion'!$D$39+C142*'Outil de gestion'!$D$40+C143*'Outil de gestion'!$D$41</f>
-        <v>0</v>
-      </c>
-      <c r="D144" s="20" t="n">
-        <f aca="false">D114*'Outil de gestion'!$D$8+D115*'Outil de gestion'!$D$9+D116*'Outil de gestion'!$D$10+D117*'Outil de gestion'!$D$11+D118*'Outil de gestion'!$D$12+D119*'Outil de gestion'!$D$13+D120*'Outil de gestion'!$D$15+D121*'Outil de gestion'!$D$16+D122*'Outil de gestion'!$D$17+D123*'Outil de gestion'!$D$18+D124*'Outil de gestion'!$D$19+D125*'Outil de gestion'!$D$20+D126*'Outil de gestion'!$D$21+D127*'Outil de gestion'!$D$22+D128*'Outil de gestion'!$D$24+D129*'Outil de gestion'!$D$25+D130*'Outil de gestion'!$D$26+D131*'Outil de gestion'!$D$27+D132*'Outil de gestion'!$D$28+D133*'Outil de gestion'!$D$29+D134*'Outil de gestion'!$D$31+D135*'Outil de gestion'!$D$32+D136*'Outil de gestion'!$D$33+D137*'Outil de gestion'!$D$34+D138*'Outil de gestion'!$D$35+D139*'Outil de gestion'!$D$37+D140*'Outil de gestion'!$D$38+D141*'Outil de gestion'!$D$39+D142*'Outil de gestion'!$D$40+D143*'Outil de gestion'!$D$41</f>
-        <v>0</v>
-      </c>
-      <c r="E144" s="20" t="n">
-        <f aca="false">E114*'Outil de gestion'!$D$8+E115*'Outil de gestion'!$D$9+E116*'Outil de gestion'!$D$10+E117*'Outil de gestion'!$D$11+E118*'Outil de gestion'!$D$12+E119*'Outil de gestion'!$D$13+E120*'Outil de gestion'!$D$15+E121*'Outil de gestion'!$D$16+E122*'Outil de gestion'!$D$17+E123*'Outil de gestion'!$D$18+E124*'Outil de gestion'!$D$19+E125*'Outil de gestion'!$D$20+E126*'Outil de gestion'!$D$21+E127*'Outil de gestion'!$D$22+E128*'Outil de gestion'!$D$24+E129*'Outil de gestion'!$D$25+E130*'Outil de gestion'!$D$26+E131*'Outil de gestion'!$D$27+E132*'Outil de gestion'!$D$28+E133*'Outil de gestion'!$D$29+E134*'Outil de gestion'!$D$31+E135*'Outil de gestion'!$D$32+E136*'Outil de gestion'!$D$33+E137*'Outil de gestion'!$D$34+E138*'Outil de gestion'!$D$35+E139*'Outil de gestion'!$D$37+E140*'Outil de gestion'!$D$38+E141*'Outil de gestion'!$D$39+E142*'Outil de gestion'!$D$40+E143*'Outil de gestion'!$D$41</f>
+      <c r="B144" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C144" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="2"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="C145" s="16" t="n">
-        <f aca="false">SUM(C114:C143)</f>
-        <v>0</v>
-      </c>
-      <c r="D145" s="16" t="n">
-        <f aca="false">SUM(D114:D143)</f>
-        <v>0</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <f aca="false">SUM(E114:E143)</f>
+        <v>271</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C145" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="2"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C146" s="20" t="n">
-        <f aca="false">IF(C109="Oui",'Outil de gestion'!$D$6+C144*(1+C111),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D146" s="20" t="n">
-        <f aca="false">IF(D109="Oui",'Outil de gestion'!$D$6+D144*(1+D111),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E146" s="20" t="n">
-        <f aca="false">IF(E109="Oui",'Outil de gestion'!$D$6+E144*(1+E111),0)</f>
+      <c r="A146" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C146" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="2"/>
     </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C147" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2"/>
+    </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
+      <c r="A148" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C148" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B149" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="C149" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" s="15" t="n">
+      <c r="A149" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C149" s="20" t="n">
+        <f aca="false">C114*'Outil de gestion'!$D$8+C115*'Outil de gestion'!$D$9+C116*'Outil de gestion'!$D$10+C117*'Outil de gestion'!$D$11+C118*'Outil de gestion'!$D$12+C119*'Outil de gestion'!$D$13+C120*'Outil de gestion'!$D$15+C121*'Outil de gestion'!$D$16+C122*'Outil de gestion'!$D$17+C123*'Outil de gestion'!$D$18+C124*'Outil de gestion'!$D$19+C125*'Outil de gestion'!$D$20+C126*'Outil de gestion'!$D$21+C127*'Outil de gestion'!$D$22+C128*'Outil de gestion'!$D$24+C129*'Outil de gestion'!$D$25+C130*'Outil de gestion'!$D$26+C131*'Outil de gestion'!$D$27+C132*'Outil de gestion'!$D$28+C133*'Outil de gestion'!$D$29+C134*'Outil de gestion'!$D$31+C135*'Outil de gestion'!$D$32+C136*'Outil de gestion'!$D$33+C137*'Outil de gestion'!$D$34+C138*'Outil de gestion'!$D$35+C139*'Outil de gestion'!$D$37+C140*'Outil de gestion'!$D$38+C141*'Outil de gestion'!$D$39+C142*'Outil de gestion'!$D$40+C143*'Outil de gestion'!$D$41+C144*'Outil de gestion'!$D$43+C145*'Outil de gestion'!$D$44+C146*'Outil de gestion'!$D$45+C147*'Outil de gestion'!$D$46+C148*'Outil de gestion'!$D$47</f>
+        <v>0</v>
+      </c>
+      <c r="D149" s="20" t="n">
+        <f aca="false">D114*'Outil de gestion'!$D$8+D115*'Outil de gestion'!$D$9+D116*'Outil de gestion'!$D$10+D117*'Outil de gestion'!$D$11+D118*'Outil de gestion'!$D$12+D119*'Outil de gestion'!$D$13+D120*'Outil de gestion'!$D$15+D121*'Outil de gestion'!$D$16+D122*'Outil de gestion'!$D$17+D123*'Outil de gestion'!$D$18+D124*'Outil de gestion'!$D$19+D125*'Outil de gestion'!$D$20+D126*'Outil de gestion'!$D$21+D127*'Outil de gestion'!$D$22+D128*'Outil de gestion'!$D$24+D129*'Outil de gestion'!$D$25+D130*'Outil de gestion'!$D$26+D131*'Outil de gestion'!$D$27+D132*'Outil de gestion'!$D$28+D133*'Outil de gestion'!$D$29+D134*'Outil de gestion'!$D$31+D135*'Outil de gestion'!$D$32+D136*'Outil de gestion'!$D$33+D137*'Outil de gestion'!$D$34+D138*'Outil de gestion'!$D$35+D139*'Outil de gestion'!$D$37+D140*'Outil de gestion'!$D$38+D141*'Outil de gestion'!$D$39+D142*'Outil de gestion'!$D$40+D143*'Outil de gestion'!$D$41+D144*'Outil de gestion'!$D$43+D145*'Outil de gestion'!$D$44+D146*'Outil de gestion'!$D$45+D147*'Outil de gestion'!$D$46+D148*'Outil de gestion'!$D$47</f>
+        <v>0</v>
+      </c>
+      <c r="E149" s="20" t="n">
+        <f aca="false">E114*'Outil de gestion'!$D$8+E115*'Outil de gestion'!$D$9+E116*'Outil de gestion'!$D$10+E117*'Outil de gestion'!$D$11+E118*'Outil de gestion'!$D$12+E119*'Outil de gestion'!$D$13+E120*'Outil de gestion'!$D$15+E121*'Outil de gestion'!$D$16+E122*'Outil de gestion'!$D$17+E123*'Outil de gestion'!$D$18+E124*'Outil de gestion'!$D$19+E125*'Outil de gestion'!$D$20+E126*'Outil de gestion'!$D$21+E127*'Outil de gestion'!$D$22+E128*'Outil de gestion'!$D$24+E129*'Outil de gestion'!$D$25+E130*'Outil de gestion'!$D$26+E131*'Outil de gestion'!$D$27+E132*'Outil de gestion'!$D$28+E133*'Outil de gestion'!$D$29+E134*'Outil de gestion'!$D$31+E135*'Outil de gestion'!$D$32+E136*'Outil de gestion'!$D$33+E137*'Outil de gestion'!$D$34+E138*'Outil de gestion'!$D$35+E139*'Outil de gestion'!$D$37+E140*'Outil de gestion'!$D$38+E141*'Outil de gestion'!$D$39+E142*'Outil de gestion'!$D$40+E143*'Outil de gestion'!$D$41+E144*'Outil de gestion'!$D$43+E145*'Outil de gestion'!$D$44+E146*'Outil de gestion'!$D$45+E147*'Outil de gestion'!$D$46+E148*'Outil de gestion'!$D$47</f>
         <v>0</v>
       </c>
       <c r="F149" s="2"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="C150" s="16" t="n">
+        <f aca="false">SUM(C114:C148)</f>
+        <v>0</v>
+      </c>
+      <c r="D150" s="16" t="n">
+        <f aca="false">SUM(D114:D148)</f>
+        <v>0</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <f aca="false">SUM(E114:E148)</f>
         <v>0</v>
       </c>
       <c r="F150" s="2"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="C151" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" s="15" t="n">
+      <c r="A151" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C151" s="20" t="n">
+        <f aca="false">IF(C109="Oui",'Outil de gestion'!$D$6+C149*(1+C111),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D151" s="20" t="n">
+        <f aca="false">IF(D109="Oui",'Outil de gestion'!$D$6+D149*(1+D111),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E151" s="20" t="n">
+        <f aca="false">IF(E109="Oui",'Outil de gestion'!$D$6+E149*(1+E111),0)</f>
         <v>0</v>
       </c>
       <c r="F151" s="2"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C152" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="2"/>
-    </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="B153" s="11" t="s">
+      <c r="A153" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C153" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="2"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
@@ -6588,449 +6636,451 @@
       <c r="F157" s="2"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="19" t="s">
+      <c r="A158" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C158" s="20" t="n">
-        <f aca="false">C149*'Outil de gestion'!$D$43+C150*'Outil de gestion'!$D$44+C151*'Outil de gestion'!$D$45+C152*'Outil de gestion'!$D$46+C153*'Outil de gestion'!$D$47+C154*'Outil de gestion'!$D$48+C155*'Outil de gestion'!$D$49+C156*'Outil de gestion'!$D$50+C157*'Outil de gestion'!$D$51</f>
-        <v>0</v>
-      </c>
-      <c r="D158" s="20" t="n">
-        <f aca="false">D149*'Outil de gestion'!$D$43+D150*'Outil de gestion'!$D$44+D151*'Outil de gestion'!$D$45+D152*'Outil de gestion'!$D$46+D153*'Outil de gestion'!$D$47+D154*'Outil de gestion'!$D$48+D155*'Outil de gestion'!$D$49+D156*'Outil de gestion'!$D$50+D157*'Outil de gestion'!$D$51</f>
-        <v>0</v>
-      </c>
-      <c r="E158" s="20" t="n">
-        <f aca="false">E149*'Outil de gestion'!$D$43+E150*'Outil de gestion'!$D$44+E151*'Outil de gestion'!$D$45+E152*'Outil de gestion'!$D$46+E153*'Outil de gestion'!$D$47+E154*'Outil de gestion'!$D$48+E155*'Outil de gestion'!$D$49+E156*'Outil de gestion'!$D$50+E157*'Outil de gestion'!$D$51</f>
+      <c r="B158" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C158" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F158" s="2"/>
     </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C159" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2"/>
+    </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
-      <c r="F160" s="9"/>
+      <c r="A160" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C160" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B161" s="11"/>
-      <c r="C161" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D161" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E161" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C161" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B162" s="11"/>
-      <c r="C162" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C162" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="2"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C163" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="15" t="n">
+      <c r="A163" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="C163" s="20" t="n">
+        <f aca="false">C154*'Outil de gestion'!$D$49+C155*'Outil de gestion'!$D$50+C156*'Outil de gestion'!$D$51+C157*'Outil de gestion'!$D$52+C158*'Outil de gestion'!$D$53+C159*'Outil de gestion'!$D$54+C160*'Outil de gestion'!$D$55+C161*'Outil de gestion'!$D$56+C162*'Outil de gestion'!$D$57</f>
+        <v>0</v>
+      </c>
+      <c r="D163" s="20" t="n">
+        <f aca="false">D154*'Outil de gestion'!$D$49+D155*'Outil de gestion'!$D$50+D156*'Outil de gestion'!$D$51+D157*'Outil de gestion'!$D$52+D158*'Outil de gestion'!$D$53+D159*'Outil de gestion'!$D$54+D160*'Outil de gestion'!$D$55+D161*'Outil de gestion'!$D$56+D162*'Outil de gestion'!$D$57</f>
+        <v>0</v>
+      </c>
+      <c r="E163" s="20" t="n">
+        <f aca="false">E154*'Outil de gestion'!$D$49+E155*'Outil de gestion'!$D$50+E156*'Outil de gestion'!$D$51+E157*'Outil de gestion'!$D$52+E158*'Outil de gestion'!$D$53+E159*'Outil de gestion'!$D$54+E160*'Outil de gestion'!$D$55+E161*'Outil de gestion'!$D$56+E162*'Outil de gestion'!$D$57</f>
         <v>0</v>
       </c>
       <c r="F163" s="2"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B164" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="C164" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="2"/>
-    </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B165" s="11"/>
-      <c r="C165" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E165" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F165" s="2"/>
+      <c r="A165" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B166" s="11"/>
-      <c r="C166" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="2" t="s">
         <v>303</v>
       </c>
+      <c r="B166" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C166" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C167" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="2"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="F168" s="9"/>
+      <c r="A168" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B168" s="11"/>
+      <c r="C168" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E168" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F168" s="2"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C169" s="18" t="n">
-        <f aca="false">C15+C16+C17+C18+C24+C25+C85+C47+C60+C69+C93+C106+C146+C158+C163*'Parcours client'!$D$11+C164*'Parcours client'!$D$14</f>
-        <v>4045.37931034483</v>
-      </c>
-      <c r="D169" s="18" t="n">
-        <f aca="false">D15+D16+D17+D18+D24+D25+D85+D47+D60+D69+D93+D106+D146+D158+D163*'Parcours client'!$D$11+D164*'Parcours client'!$D$14</f>
-        <v>4132</v>
-      </c>
-      <c r="E169" s="18" t="n">
-        <f aca="false">E15+E16+E17+E18+E24+E25+E85+E47+E60+E69+E93+E106+E146+E158+E163*'Parcours client'!$D$11+E164*'Parcours client'!$D$14</f>
-        <v>500</v>
-      </c>
-      <c r="F169" s="2"/>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="C170" s="18" t="n">
-        <f aca="false">C169*Paramètres!$B$6*IF(C165="Oui",1+Paramètres!$B$15,1)*(1-C166)</f>
-        <v>4045.37931034483</v>
-      </c>
-      <c r="D170" s="18" t="n">
-        <f aca="false">D169*Paramètres!$B$6*IF(D165="Oui",1+Paramètres!$B$15,1)*(1-D166)</f>
-        <v>4132</v>
-      </c>
-      <c r="E170" s="18" t="n">
-        <f aca="false">E169*Paramètres!$B$6*IF(E165="Oui",1+Paramètres!$B$15,1)*(1-E166)</f>
-        <v>500</v>
-      </c>
-      <c r="F170" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="B169" s="11"/>
+      <c r="C169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="C171" s="24" t="n">
-        <f aca="false">ROUND(C170/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>4050</v>
-      </c>
-      <c r="D171" s="24" t="n">
-        <f aca="false">ROUND(D170/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>4130</v>
-      </c>
-      <c r="E171" s="24" t="n">
-        <f aca="false">ROUND(E170/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>500</v>
-      </c>
-      <c r="F171" s="2"/>
+      <c r="A171" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="9"/>
+      <c r="F171" s="9"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C172" s="18" t="n">
-        <f aca="false">-(IF(C161="Oui",'Parcours client'!$D$7,0)+IF(C162="Oui",'Parcours client'!$D$8,0))</f>
-        <v>-0</v>
+        <f aca="false">C15+C16+C17+C18+C24+C25+C85+C47+C60+C69+C93+C106+C151+C163+C166*'Parcours client'!$D$11+C167*'Parcours client'!$D$14</f>
+        <v>4045.37931034483</v>
       </c>
       <c r="D172" s="18" t="n">
-        <f aca="false">-(IF(D161="Oui",'Parcours client'!$D$7,0)+IF(D162="Oui",'Parcours client'!$D$8,0))</f>
-        <v>-0</v>
+        <f aca="false">D15+D16+D17+D18+D24+D25+D85+D47+D60+D69+D93+D106+D151+D163+D166*'Parcours client'!$D$11+D167*'Parcours client'!$D$14</f>
+        <v>4132</v>
       </c>
       <c r="E172" s="18" t="n">
-        <f aca="false">-(IF(E161="Oui",'Parcours client'!$D$7,0)+IF(E162="Oui",'Parcours client'!$D$8,0))</f>
-        <v>-45</v>
+        <f aca="false">E15+E16+E17+E18+E24+E25+E85+E47+E60+E69+E93+E106+E151+E163+E166*'Parcours client'!$D$11+E167*'Parcours client'!$D$14</f>
+        <v>500</v>
       </c>
       <c r="F172" s="2"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="C173" s="20" t="n">
-        <f aca="false">C171+C172</f>
+      <c r="A173" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C173" s="18" t="n">
+        <f aca="false">C172*Paramètres!$B$6*IF(C168="Oui",1+Paramètres!$B$15,1)*(1-C169)</f>
+        <v>4045.37931034483</v>
+      </c>
+      <c r="D173" s="18" t="n">
+        <f aca="false">D172*Paramètres!$B$6*IF(D168="Oui",1+Paramètres!$B$15,1)*(1-D169)</f>
+        <v>4132</v>
+      </c>
+      <c r="E173" s="18" t="n">
+        <f aca="false">E172*Paramètres!$B$6*IF(E168="Oui",1+Paramètres!$B$15,1)*(1-E169)</f>
+        <v>500</v>
+      </c>
+      <c r="F173" s="2"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C174" s="24" t="n">
+        <f aca="false">ROUND(C173/Paramètres!$B$9,0)*Paramètres!$B$9</f>
         <v>4050</v>
       </c>
-      <c r="D173" s="20" t="n">
-        <f aca="false">D171+D172</f>
+      <c r="D174" s="24" t="n">
+        <f aca="false">ROUND(D173/Paramètres!$B$9,0)*Paramètres!$B$9</f>
         <v>4130</v>
       </c>
-      <c r="E173" s="20" t="n">
-        <f aca="false">E171+E172</f>
-        <v>455</v>
-      </c>
-      <c r="F173" s="2"/>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C174" s="18" t="n">
-        <f aca="false">ROUND(C173*Paramètres!$B$14,0)</f>
+      <c r="E174" s="24" t="n">
+        <f aca="false">ROUND(E173/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+        <v>500</v>
+      </c>
+      <c r="F174" s="2"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C175" s="18" t="n">
+        <f aca="false">ROUND(C174*Paramètres!$B$14,0)</f>
         <v>1620</v>
       </c>
-      <c r="D174" s="18" t="n">
-        <f aca="false">ROUND(D173*Paramètres!$B$14,0)</f>
+      <c r="D175" s="18" t="n">
+        <f aca="false">ROUND(D174*Paramètres!$B$14,0)</f>
         <v>1652</v>
       </c>
-      <c r="E174" s="18" t="n">
-        <f aca="false">ROUND(E173*Paramètres!$B$14,0)</f>
-        <v>182</v>
-      </c>
-      <c r="F174" s="2"/>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="C175" s="26" t="n">
-        <f aca="false">ROUND(C171*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>3650</v>
-      </c>
-      <c r="D175" s="26" t="n">
-        <f aca="false">ROUND(D171*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>3720</v>
-      </c>
-      <c r="E175" s="26" t="n">
-        <f aca="false">ROUND(E171*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
-        <v>450</v>
+      <c r="E175" s="18" t="n">
+        <f aca="false">ROUND(E174*Paramètres!$B$14,0)</f>
+        <v>200</v>
       </c>
       <c r="F175" s="2"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="25" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C176" s="26" t="n">
-        <f aca="false">ROUND(C171*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+        <f aca="false">ROUND(C174*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+        <v>3650</v>
+      </c>
+      <c r="D176" s="26" t="n">
+        <f aca="false">ROUND(D174*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+        <v>3720</v>
+      </c>
+      <c r="E176" s="26" t="n">
+        <f aca="false">ROUND(E174*Paramètres!$B$7/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+        <v>450</v>
+      </c>
+      <c r="F176" s="2"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C177" s="26" t="n">
+        <f aca="false">ROUND(C174*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
         <v>4660</v>
       </c>
-      <c r="D176" s="26" t="n">
-        <f aca="false">ROUND(D171*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+      <c r="D177" s="26" t="n">
+        <f aca="false">ROUND(D174*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
         <v>4750</v>
       </c>
-      <c r="E176" s="26" t="n">
-        <f aca="false">ROUND(E171*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
+      <c r="E177" s="26" t="n">
+        <f aca="false">ROUND(E174*Paramètres!$B$8/Paramètres!$B$9,0)*Paramètres!$B$9</f>
         <v>580</v>
       </c>
-      <c r="F176" s="2"/>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C177" s="27" t="str">
-        <f aca="false">IF(C171&gt;=Paramètres!$B$18,"Oui","Non")</f>
+      <c r="F177" s="2"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C178" s="27" t="str">
+        <f aca="false">IF(C174&gt;=Paramètres!$B$18,"Oui","Non")</f>
         <v>Oui</v>
       </c>
-      <c r="D177" s="27" t="str">
-        <f aca="false">IF(D171&gt;=Paramètres!$B$18,"Oui","Non")</f>
+      <c r="D178" s="27" t="str">
+        <f aca="false">IF(D174&gt;=Paramètres!$B$18,"Oui","Non")</f>
         <v>Oui</v>
       </c>
-      <c r="E177" s="27" t="str">
-        <f aca="false">IF(E171&gt;=Paramètres!$B$18,"Oui","Non")</f>
+      <c r="E178" s="27" t="str">
+        <f aca="false">IF(E174&gt;=Paramètres!$B$18,"Oui","Non")</f>
         <v>Non</v>
       </c>
-      <c r="F177" s="2"/>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
+      <c r="F178" s="2"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="C180" s="28" t="n">
-        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(C7,'Création site'!$A$6:$A$10,0))+C14*(C8*'Création site'!$G$7+C9*'Création site'!$G$8+C10*'Création site'!$G$9+C11*'Création site'!$G$10)+C12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(C21,Référencement!$A$6:$A$10,0))+C23*INDEX(Référencement!$G$6:$G$10,MATCH(C21,Référencement!$A$6:$A$10,0))+C12*INDEX(Référencement!$I$6:$I$10,MATCH(C21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(C22,Référencement!$A$14:$A$16,0))+C23*INDEX(Référencement!$G$14:$G$16,MATCH(C22,Référencement!$A$14:$A$16,0))+C28*'Création site'!$E$18+C29*'Création site'!$E$19+C30*'Création site'!$E$20+C31*'Création site'!$E$21+C32*'Création site'!$E$22+C33*'Création site'!$E$23+C34*'Création site'!$E$24+C35*'Création site'!$E$25+C36*'Création site'!$E$26+C37*'Création site'!$E$27+C38*'Création site'!$E$28+C39*'Création site'!$E$29+C40*'Création site'!$E$30+C41*'Création site'!$E$31+C42*'Création site'!$E$32+C43*'Création site'!$E$33+C44*'Création site'!$E$34+C45*'Création site'!$E$35+C46*'Création site'!$E$36+C50*'Création site'!$E$38+C51*'Création site'!$E$39+C52*'Création site'!$E$40+C53*'Création site'!$E$41+C54*'Création site'!$E$42+C55*'Création site'!$E$43+C56*'Création site'!$E$44+C57*'Création site'!$E$45+C58*'Création site'!$E$46+C59*'Création site'!$E$47+C63*'Création site'!$E$49+C64*'Création site'!$E$50+C65*'Création site'!$E$51+C66*'Création site'!$E$52+C67*'Création site'!$E$53+C68*'Création site'!$E$54+C72*Référencement!$E$20+C73*Référencement!$E$21+C74*Référencement!$E$22+C75*Référencement!$E$23+C76*Référencement!$E$24+C77*Référencement!$E$25+C78*Référencement!$E$26+C79*Référencement!$E$27+C80*Référencement!$E$28+C81*Référencement!$E$29+C82*Référencement!$E$30+C83*Référencement!$E$31+C84*Référencement!$E$32+C96*Boutique!$E$13+C97*Boutique!$E$14+C98*Boutique!$E$15+C99*Boutique!$E$16+C100*Boutique!$E$17+C101*Boutique!$E$18+C102*Boutique!$E$19+C103*Boutique!$E$20+C104*Boutique!$E$21+C105*Boutique!$E$22+C149*'Outil de gestion'!$E$43+C150*'Outil de gestion'!$E$44+C151*'Outil de gestion'!$E$45+C152*'Outil de gestion'!$E$46+C153*'Outil de gestion'!$E$47+C154*'Outil de gestion'!$E$48+C155*'Outil de gestion'!$E$49+C156*'Outil de gestion'!$E$50+C157*'Outil de gestion'!$E$51+IF(C88="Oui",Boutique!$E$6+IF(C90="Oui",Boutique!$E$9,C89*Boutique!$E$8),0)+IF(C109="Oui",'Outil de gestion'!$E$6,0)+C114*'Outil de gestion'!$E$8+C115*'Outil de gestion'!$E$9+C116*'Outil de gestion'!$E$10+C117*'Outil de gestion'!$E$11+C118*'Outil de gestion'!$E$12+C119*'Outil de gestion'!$E$13+C120*'Outil de gestion'!$E$15+C121*'Outil de gestion'!$E$16+C122*'Outil de gestion'!$E$17+C123*'Outil de gestion'!$E$18+C124*'Outil de gestion'!$E$19+C125*'Outil de gestion'!$E$20+C126*'Outil de gestion'!$E$21+C127*'Outil de gestion'!$E$22+C128*'Outil de gestion'!$E$24+C129*'Outil de gestion'!$E$25+C130*'Outil de gestion'!$E$26+C131*'Outil de gestion'!$E$27+C132*'Outil de gestion'!$E$28+C133*'Outil de gestion'!$E$29+C134*'Outil de gestion'!$E$31+C135*'Outil de gestion'!$E$32+C136*'Outil de gestion'!$E$33+C137*'Outil de gestion'!$E$34+C138*'Outil de gestion'!$E$35+C139*'Outil de gestion'!$E$37+C140*'Outil de gestion'!$E$38+C141*'Outil de gestion'!$E$39+C142*'Outil de gestion'!$E$40+C143*'Outil de gestion'!$E$41+C163</f>
-        <v>74.5706896551724</v>
-      </c>
-      <c r="D180" s="28" t="n">
-        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(D7,'Création site'!$A$6:$A$10,0))+D14*(D8*'Création site'!$G$7+D9*'Création site'!$G$8+D10*'Création site'!$G$9+D11*'Création site'!$G$10)+D12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(D21,Référencement!$A$6:$A$10,0))+D23*INDEX(Référencement!$G$6:$G$10,MATCH(D21,Référencement!$A$6:$A$10,0))+D12*INDEX(Référencement!$I$6:$I$10,MATCH(D21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(D22,Référencement!$A$14:$A$16,0))+D23*INDEX(Référencement!$G$14:$G$16,MATCH(D22,Référencement!$A$14:$A$16,0))+D28*'Création site'!$E$18+D29*'Création site'!$E$19+D30*'Création site'!$E$20+D31*'Création site'!$E$21+D32*'Création site'!$E$22+D33*'Création site'!$E$23+D34*'Création site'!$E$24+D35*'Création site'!$E$25+D36*'Création site'!$E$26+D37*'Création site'!$E$27+D38*'Création site'!$E$28+D39*'Création site'!$E$29+D40*'Création site'!$E$30+D41*'Création site'!$E$31+D42*'Création site'!$E$32+D43*'Création site'!$E$33+D44*'Création site'!$E$34+D45*'Création site'!$E$35+D46*'Création site'!$E$36+D50*'Création site'!$E$38+D51*'Création site'!$E$39+D52*'Création site'!$E$40+D53*'Création site'!$E$41+D54*'Création site'!$E$42+D55*'Création site'!$E$43+D56*'Création site'!$E$44+D57*'Création site'!$E$45+D58*'Création site'!$E$46+D59*'Création site'!$E$47+D63*'Création site'!$E$49+D64*'Création site'!$E$50+D65*'Création site'!$E$51+D66*'Création site'!$E$52+D67*'Création site'!$E$53+D68*'Création site'!$E$54+D72*Référencement!$E$20+D73*Référencement!$E$21+D74*Référencement!$E$22+D75*Référencement!$E$23+D76*Référencement!$E$24+D77*Référencement!$E$25+D78*Référencement!$E$26+D79*Référencement!$E$27+D80*Référencement!$E$28+D81*Référencement!$E$29+D82*Référencement!$E$30+D83*Référencement!$E$31+D84*Référencement!$E$32+D96*Boutique!$E$13+D97*Boutique!$E$14+D98*Boutique!$E$15+D99*Boutique!$E$16+D100*Boutique!$E$17+D101*Boutique!$E$18+D102*Boutique!$E$19+D103*Boutique!$E$20+D104*Boutique!$E$21+D105*Boutique!$E$22+D149*'Outil de gestion'!$E$43+D150*'Outil de gestion'!$E$44+D151*'Outil de gestion'!$E$45+D152*'Outil de gestion'!$E$46+D153*'Outil de gestion'!$E$47+D154*'Outil de gestion'!$E$48+D155*'Outil de gestion'!$E$49+D156*'Outil de gestion'!$E$50+D157*'Outil de gestion'!$E$51+IF(D88="Oui",Boutique!$E$6+IF(D90="Oui",Boutique!$E$9,D89*Boutique!$E$8),0)+IF(D109="Oui",'Outil de gestion'!$E$6,0)+D114*'Outil de gestion'!$E$8+D115*'Outil de gestion'!$E$9+D116*'Outil de gestion'!$E$10+D117*'Outil de gestion'!$E$11+D118*'Outil de gestion'!$E$12+D119*'Outil de gestion'!$E$13+D120*'Outil de gestion'!$E$15+D121*'Outil de gestion'!$E$16+D122*'Outil de gestion'!$E$17+D123*'Outil de gestion'!$E$18+D124*'Outil de gestion'!$E$19+D125*'Outil de gestion'!$E$20+D126*'Outil de gestion'!$E$21+D127*'Outil de gestion'!$E$22+D128*'Outil de gestion'!$E$24+D129*'Outil de gestion'!$E$25+D130*'Outil de gestion'!$E$26+D131*'Outil de gestion'!$E$27+D132*'Outil de gestion'!$E$28+D133*'Outil de gestion'!$E$29+D134*'Outil de gestion'!$E$31+D135*'Outil de gestion'!$E$32+D136*'Outil de gestion'!$E$33+D137*'Outil de gestion'!$E$34+D138*'Outil de gestion'!$E$35+D139*'Outil de gestion'!$E$37+D140*'Outil de gestion'!$E$38+D141*'Outil de gestion'!$E$39+D142*'Outil de gestion'!$E$40+D143*'Outil de gestion'!$E$41+D163</f>
-        <v>78.5714285714286</v>
-      </c>
-      <c r="E180" s="28" t="n">
-        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(E7,'Création site'!$A$6:$A$10,0))+E14*(E8*'Création site'!$G$7+E9*'Création site'!$G$8+E10*'Création site'!$G$9+E11*'Création site'!$G$10)+E12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(E21,Référencement!$A$6:$A$10,0))+E23*INDEX(Référencement!$G$6:$G$10,MATCH(E21,Référencement!$A$6:$A$10,0))+E12*INDEX(Référencement!$I$6:$I$10,MATCH(E21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(E22,Référencement!$A$14:$A$16,0))+E23*INDEX(Référencement!$G$14:$G$16,MATCH(E22,Référencement!$A$14:$A$16,0))+E28*'Création site'!$E$18+E29*'Création site'!$E$19+E30*'Création site'!$E$20+E31*'Création site'!$E$21+E32*'Création site'!$E$22+E33*'Création site'!$E$23+E34*'Création site'!$E$24+E35*'Création site'!$E$25+E36*'Création site'!$E$26+E37*'Création site'!$E$27+E38*'Création site'!$E$28+E39*'Création site'!$E$29+E40*'Création site'!$E$30+E41*'Création site'!$E$31+E42*'Création site'!$E$32+E43*'Création site'!$E$33+E44*'Création site'!$E$34+E45*'Création site'!$E$35+E46*'Création site'!$E$36+E50*'Création site'!$E$38+E51*'Création site'!$E$39+E52*'Création site'!$E$40+E53*'Création site'!$E$41+E54*'Création site'!$E$42+E55*'Création site'!$E$43+E56*'Création site'!$E$44+E57*'Création site'!$E$45+E58*'Création site'!$E$46+E59*'Création site'!$E$47+E63*'Création site'!$E$49+E64*'Création site'!$E$50+E65*'Création site'!$E$51+E66*'Création site'!$E$52+E67*'Création site'!$E$53+E68*'Création site'!$E$54+E72*Référencement!$E$20+E73*Référencement!$E$21+E74*Référencement!$E$22+E75*Référencement!$E$23+E76*Référencement!$E$24+E77*Référencement!$E$25+E78*Référencement!$E$26+E79*Référencement!$E$27+E80*Référencement!$E$28+E81*Référencement!$E$29+E82*Référencement!$E$30+E83*Référencement!$E$31+E84*Référencement!$E$32+E96*Boutique!$E$13+E97*Boutique!$E$14+E98*Boutique!$E$15+E99*Boutique!$E$16+E100*Boutique!$E$17+E101*Boutique!$E$18+E102*Boutique!$E$19+E103*Boutique!$E$20+E104*Boutique!$E$21+E105*Boutique!$E$22+E149*'Outil de gestion'!$E$43+E150*'Outil de gestion'!$E$44+E151*'Outil de gestion'!$E$45+E152*'Outil de gestion'!$E$46+E153*'Outil de gestion'!$E$47+E154*'Outil de gestion'!$E$48+E155*'Outil de gestion'!$E$49+E156*'Outil de gestion'!$E$50+E157*'Outil de gestion'!$E$51+IF(E88="Oui",Boutique!$E$6+IF(E90="Oui",Boutique!$E$9,E89*Boutique!$E$8),0)+IF(E109="Oui",'Outil de gestion'!$E$6,0)+E114*'Outil de gestion'!$E$8+E115*'Outil de gestion'!$E$9+E116*'Outil de gestion'!$E$10+E117*'Outil de gestion'!$E$11+E118*'Outil de gestion'!$E$12+E119*'Outil de gestion'!$E$13+E120*'Outil de gestion'!$E$15+E121*'Outil de gestion'!$E$16+E122*'Outil de gestion'!$E$17+E123*'Outil de gestion'!$E$18+E124*'Outil de gestion'!$E$19+E125*'Outil de gestion'!$E$20+E126*'Outil de gestion'!$E$21+E127*'Outil de gestion'!$E$22+E128*'Outil de gestion'!$E$24+E129*'Outil de gestion'!$E$25+E130*'Outil de gestion'!$E$26+E131*'Outil de gestion'!$E$27+E132*'Outil de gestion'!$E$28+E133*'Outil de gestion'!$E$29+E134*'Outil de gestion'!$E$31+E135*'Outil de gestion'!$E$32+E136*'Outil de gestion'!$E$33+E137*'Outil de gestion'!$E$34+E138*'Outil de gestion'!$E$35+E139*'Outil de gestion'!$E$37+E140*'Outil de gestion'!$E$38+E141*'Outil de gestion'!$E$39+E142*'Outil de gestion'!$E$40+E143*'Outil de gestion'!$E$41+E163</f>
-        <v>10</v>
-      </c>
-      <c r="F180" s="2"/>
+      <c r="A180" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C181" s="18" t="n">
-        <f aca="false">IF(C180&gt;0,C171/C180,0)</f>
-        <v>54.3108829853645</v>
-      </c>
-      <c r="D181" s="18" t="n">
-        <f aca="false">IF(D180&gt;0,D171/D180,0)</f>
-        <v>52.5636363636364</v>
-      </c>
-      <c r="E181" s="18" t="n">
-        <f aca="false">IF(E180&gt;0,E171/E180,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>317</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C181" s="28" t="n">
+        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(C7,'Création site'!$A$6:$A$10,0))+C14*(C8*'Création site'!$G$7+C9*'Création site'!$G$8+C10*'Création site'!$G$9+C11*'Création site'!$G$10)+C12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(C21,Référencement!$A$6:$A$10,0))+C23*INDEX(Référencement!$G$6:$G$10,MATCH(C21,Référencement!$A$6:$A$10,0))+C12*INDEX(Référencement!$I$6:$I$10,MATCH(C21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(C22,Référencement!$A$14:$A$16,0))+C23*INDEX(Référencement!$G$14:$G$16,MATCH(C22,Référencement!$A$14:$A$16,0))+C28*'Création site'!$E$18+C29*'Création site'!$E$19+C30*'Création site'!$E$20+C31*'Création site'!$E$21+C32*'Création site'!$E$22+C33*'Création site'!$E$23+C34*'Création site'!$E$24+C35*'Création site'!$E$25+C36*'Création site'!$E$26+C37*'Création site'!$E$27+C38*'Création site'!$E$28+C39*'Création site'!$E$29+C40*'Création site'!$E$30+C41*'Création site'!$E$31+C42*'Création site'!$E$32+C43*'Création site'!$E$33+C44*'Création site'!$E$34+C45*'Création site'!$E$35+C46*'Création site'!$E$36+C50*'Création site'!$E$38+C51*'Création site'!$E$39+C52*'Création site'!$E$40+C53*'Création site'!$E$41+C54*'Création site'!$E$42+C55*'Création site'!$E$43+C56*'Création site'!$E$44+C57*'Création site'!$E$45+C58*'Création site'!$E$46+C59*'Création site'!$E$47+C63*'Création site'!$E$49+C64*'Création site'!$E$50+C65*'Création site'!$E$51+C66*'Création site'!$E$52+C67*'Création site'!$E$53+C68*'Création site'!$E$54+C72*Référencement!$E$20+C73*Référencement!$E$21+C74*Référencement!$E$22+C75*Référencement!$E$23+C76*Référencement!$E$24+C77*Référencement!$E$25+C78*Référencement!$E$26+C79*Référencement!$E$27+C80*Référencement!$E$28+C81*Référencement!$E$29+C82*Référencement!$E$30+C83*Référencement!$E$31+C84*Référencement!$E$32+C96*Boutique!$E$13+C97*Boutique!$E$14+C98*Boutique!$E$15+C99*Boutique!$E$16+C100*Boutique!$E$17+C101*Boutique!$E$18+C102*Boutique!$E$19+C103*Boutique!$E$20+C104*Boutique!$E$21+C105*Boutique!$E$22+C154*'Outil de gestion'!$E$49+C155*'Outil de gestion'!$E$50+C156*'Outil de gestion'!$E$51+C157*'Outil de gestion'!$E$52+C158*'Outil de gestion'!$E$53+C159*'Outil de gestion'!$E$54+C160*'Outil de gestion'!$E$55+C161*'Outil de gestion'!$E$56+C162*'Outil de gestion'!$E$57+IF(C88="Oui",Boutique!$E$6+IF(C90="Oui",Boutique!$E$9,C89*Boutique!$E$8),0)+IF(C109="Oui",'Outil de gestion'!$E$6,0)+C114*'Outil de gestion'!$E$8+C115*'Outil de gestion'!$E$9+C116*'Outil de gestion'!$E$10+C117*'Outil de gestion'!$E$11+C118*'Outil de gestion'!$E$12+C119*'Outil de gestion'!$E$13+C120*'Outil de gestion'!$E$15+C121*'Outil de gestion'!$E$16+C122*'Outil de gestion'!$E$17+C123*'Outil de gestion'!$E$18+C124*'Outil de gestion'!$E$19+C125*'Outil de gestion'!$E$20+C126*'Outil de gestion'!$E$21+C127*'Outil de gestion'!$E$22+C128*'Outil de gestion'!$E$24+C129*'Outil de gestion'!$E$25+C130*'Outil de gestion'!$E$26+C131*'Outil de gestion'!$E$27+C132*'Outil de gestion'!$E$28+C133*'Outil de gestion'!$E$29+C134*'Outil de gestion'!$E$31+C135*'Outil de gestion'!$E$32+C136*'Outil de gestion'!$E$33+C137*'Outil de gestion'!$E$34+C138*'Outil de gestion'!$E$35+C139*'Outil de gestion'!$E$37+C140*'Outil de gestion'!$E$38+C141*'Outil de gestion'!$E$39+C142*'Outil de gestion'!$E$40+C143*'Outil de gestion'!$E$41+C144*'Outil de gestion'!$E$43+C145*'Outil de gestion'!$E$44+C146*'Outil de gestion'!$E$45+C147*'Outil de gestion'!$E$46+C148*'Outil de gestion'!$E$47+C166</f>
+        <v>74.5706896551724</v>
+      </c>
+      <c r="D181" s="28" t="n">
+        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(D7,'Création site'!$A$6:$A$10,0))+D14*(D8*'Création site'!$G$7+D9*'Création site'!$G$8+D10*'Création site'!$G$9+D11*'Création site'!$G$10)+D12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(D21,Référencement!$A$6:$A$10,0))+D23*INDEX(Référencement!$G$6:$G$10,MATCH(D21,Référencement!$A$6:$A$10,0))+D12*INDEX(Référencement!$I$6:$I$10,MATCH(D21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(D22,Référencement!$A$14:$A$16,0))+D23*INDEX(Référencement!$G$14:$G$16,MATCH(D22,Référencement!$A$14:$A$16,0))+D28*'Création site'!$E$18+D29*'Création site'!$E$19+D30*'Création site'!$E$20+D31*'Création site'!$E$21+D32*'Création site'!$E$22+D33*'Création site'!$E$23+D34*'Création site'!$E$24+D35*'Création site'!$E$25+D36*'Création site'!$E$26+D37*'Création site'!$E$27+D38*'Création site'!$E$28+D39*'Création site'!$E$29+D40*'Création site'!$E$30+D41*'Création site'!$E$31+D42*'Création site'!$E$32+D43*'Création site'!$E$33+D44*'Création site'!$E$34+D45*'Création site'!$E$35+D46*'Création site'!$E$36+D50*'Création site'!$E$38+D51*'Création site'!$E$39+D52*'Création site'!$E$40+D53*'Création site'!$E$41+D54*'Création site'!$E$42+D55*'Création site'!$E$43+D56*'Création site'!$E$44+D57*'Création site'!$E$45+D58*'Création site'!$E$46+D59*'Création site'!$E$47+D63*'Création site'!$E$49+D64*'Création site'!$E$50+D65*'Création site'!$E$51+D66*'Création site'!$E$52+D67*'Création site'!$E$53+D68*'Création site'!$E$54+D72*Référencement!$E$20+D73*Référencement!$E$21+D74*Référencement!$E$22+D75*Référencement!$E$23+D76*Référencement!$E$24+D77*Référencement!$E$25+D78*Référencement!$E$26+D79*Référencement!$E$27+D80*Référencement!$E$28+D81*Référencement!$E$29+D82*Référencement!$E$30+D83*Référencement!$E$31+D84*Référencement!$E$32+D96*Boutique!$E$13+D97*Boutique!$E$14+D98*Boutique!$E$15+D99*Boutique!$E$16+D100*Boutique!$E$17+D101*Boutique!$E$18+D102*Boutique!$E$19+D103*Boutique!$E$20+D104*Boutique!$E$21+D105*Boutique!$E$22+D154*'Outil de gestion'!$E$49+D155*'Outil de gestion'!$E$50+D156*'Outil de gestion'!$E$51+D157*'Outil de gestion'!$E$52+D158*'Outil de gestion'!$E$53+D159*'Outil de gestion'!$E$54+D160*'Outil de gestion'!$E$55+D161*'Outil de gestion'!$E$56+D162*'Outil de gestion'!$E$57+IF(D88="Oui",Boutique!$E$6+IF(D90="Oui",Boutique!$E$9,D89*Boutique!$E$8),0)+IF(D109="Oui",'Outil de gestion'!$E$6,0)+D114*'Outil de gestion'!$E$8+D115*'Outil de gestion'!$E$9+D116*'Outil de gestion'!$E$10+D117*'Outil de gestion'!$E$11+D118*'Outil de gestion'!$E$12+D119*'Outil de gestion'!$E$13+D120*'Outil de gestion'!$E$15+D121*'Outil de gestion'!$E$16+D122*'Outil de gestion'!$E$17+D123*'Outil de gestion'!$E$18+D124*'Outil de gestion'!$E$19+D125*'Outil de gestion'!$E$20+D126*'Outil de gestion'!$E$21+D127*'Outil de gestion'!$E$22+D128*'Outil de gestion'!$E$24+D129*'Outil de gestion'!$E$25+D130*'Outil de gestion'!$E$26+D131*'Outil de gestion'!$E$27+D132*'Outil de gestion'!$E$28+D133*'Outil de gestion'!$E$29+D134*'Outil de gestion'!$E$31+D135*'Outil de gestion'!$E$32+D136*'Outil de gestion'!$E$33+D137*'Outil de gestion'!$E$34+D138*'Outil de gestion'!$E$35+D139*'Outil de gestion'!$E$37+D140*'Outil de gestion'!$E$38+D141*'Outil de gestion'!$E$39+D142*'Outil de gestion'!$E$40+D143*'Outil de gestion'!$E$41+D144*'Outil de gestion'!$E$43+D145*'Outil de gestion'!$E$44+D146*'Outil de gestion'!$E$45+D147*'Outil de gestion'!$E$46+D148*'Outil de gestion'!$E$47+D166</f>
+        <v>78.5714285714286</v>
+      </c>
+      <c r="E181" s="28" t="n">
+        <f aca="false">'Création site'!$E$14+INDEX('Création site'!$E$6:$E$10,MATCH(E7,'Création site'!$A$6:$A$10,0))+E14*(E8*'Création site'!$G$7+E9*'Création site'!$G$8+E10*'Création site'!$G$9+E11*'Création site'!$G$10)+E12*'Création site'!$E$15+INDEX(Référencement!$E$6:$E$10,MATCH(E21,Référencement!$A$6:$A$10,0))+E23*INDEX(Référencement!$G$6:$G$10,MATCH(E21,Référencement!$A$6:$A$10,0))+E12*INDEX(Référencement!$I$6:$I$10,MATCH(E21,Référencement!$A$6:$A$10,0))+INDEX(Référencement!$E$14:$E$16,MATCH(E22,Référencement!$A$14:$A$16,0))+E23*INDEX(Référencement!$G$14:$G$16,MATCH(E22,Référencement!$A$14:$A$16,0))+E28*'Création site'!$E$18+E29*'Création site'!$E$19+E30*'Création site'!$E$20+E31*'Création site'!$E$21+E32*'Création site'!$E$22+E33*'Création site'!$E$23+E34*'Création site'!$E$24+E35*'Création site'!$E$25+E36*'Création site'!$E$26+E37*'Création site'!$E$27+E38*'Création site'!$E$28+E39*'Création site'!$E$29+E40*'Création site'!$E$30+E41*'Création site'!$E$31+E42*'Création site'!$E$32+E43*'Création site'!$E$33+E44*'Création site'!$E$34+E45*'Création site'!$E$35+E46*'Création site'!$E$36+E50*'Création site'!$E$38+E51*'Création site'!$E$39+E52*'Création site'!$E$40+E53*'Création site'!$E$41+E54*'Création site'!$E$42+E55*'Création site'!$E$43+E56*'Création site'!$E$44+E57*'Création site'!$E$45+E58*'Création site'!$E$46+E59*'Création site'!$E$47+E63*'Création site'!$E$49+E64*'Création site'!$E$50+E65*'Création site'!$E$51+E66*'Création site'!$E$52+E67*'Création site'!$E$53+E68*'Création site'!$E$54+E72*Référencement!$E$20+E73*Référencement!$E$21+E74*Référencement!$E$22+E75*Référencement!$E$23+E76*Référencement!$E$24+E77*Référencement!$E$25+E78*Référencement!$E$26+E79*Référencement!$E$27+E80*Référencement!$E$28+E81*Référencement!$E$29+E82*Référencement!$E$30+E83*Référencement!$E$31+E84*Référencement!$E$32+E96*Boutique!$E$13+E97*Boutique!$E$14+E98*Boutique!$E$15+E99*Boutique!$E$16+E100*Boutique!$E$17+E101*Boutique!$E$18+E102*Boutique!$E$19+E103*Boutique!$E$20+E104*Boutique!$E$21+E105*Boutique!$E$22+E154*'Outil de gestion'!$E$49+E155*'Outil de gestion'!$E$50+E156*'Outil de gestion'!$E$51+E157*'Outil de gestion'!$E$52+E158*'Outil de gestion'!$E$53+E159*'Outil de gestion'!$E$54+E160*'Outil de gestion'!$E$55+E161*'Outil de gestion'!$E$56+E162*'Outil de gestion'!$E$57+IF(E88="Oui",Boutique!$E$6+IF(E90="Oui",Boutique!$E$9,E89*Boutique!$E$8),0)+IF(E109="Oui",'Outil de gestion'!$E$6,0)+E114*'Outil de gestion'!$E$8+E115*'Outil de gestion'!$E$9+E116*'Outil de gestion'!$E$10+E117*'Outil de gestion'!$E$11+E118*'Outil de gestion'!$E$12+E119*'Outil de gestion'!$E$13+E120*'Outil de gestion'!$E$15+E121*'Outil de gestion'!$E$16+E122*'Outil de gestion'!$E$17+E123*'Outil de gestion'!$E$18+E124*'Outil de gestion'!$E$19+E125*'Outil de gestion'!$E$20+E126*'Outil de gestion'!$E$21+E127*'Outil de gestion'!$E$22+E128*'Outil de gestion'!$E$24+E129*'Outil de gestion'!$E$25+E130*'Outil de gestion'!$E$26+E131*'Outil de gestion'!$E$27+E132*'Outil de gestion'!$E$28+E133*'Outil de gestion'!$E$29+E134*'Outil de gestion'!$E$31+E135*'Outil de gestion'!$E$32+E136*'Outil de gestion'!$E$33+E137*'Outil de gestion'!$E$34+E138*'Outil de gestion'!$E$35+E139*'Outil de gestion'!$E$37+E140*'Outil de gestion'!$E$38+E141*'Outil de gestion'!$E$39+E142*'Outil de gestion'!$E$40+E143*'Outil de gestion'!$E$41+E144*'Outil de gestion'!$E$43+E145*'Outil de gestion'!$E$44+E146*'Outil de gestion'!$E$45+E147*'Outil de gestion'!$E$46+E148*'Outil de gestion'!$E$47+E166</f>
+        <v>10</v>
+      </c>
+      <c r="F181" s="2"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="C182" s="16" t="n">
-        <f aca="false">MAX(1,ROUNDUP(C180/Paramètres!$B$16,0))</f>
-        <v>5</v>
-      </c>
-      <c r="D182" s="16" t="n">
-        <f aca="false">MAX(1,ROUNDUP(D180/Paramètres!$B$16,0))</f>
-        <v>6</v>
-      </c>
-      <c r="E182" s="16" t="n">
-        <f aca="false">MAX(1,ROUNDUP(E180/Paramètres!$B$16,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F182" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="C182" s="18" t="n">
+        <f aca="false">IF(C181&gt;0,C174/C181,0)</f>
+        <v>54.3108829853645</v>
+      </c>
+      <c r="D182" s="18" t="n">
+        <f aca="false">IF(D181&gt;0,D174/D181,0)</f>
+        <v>52.5636363636364</v>
+      </c>
+      <c r="E182" s="18" t="n">
+        <f aca="false">IF(E181&gt;0,E174/E181,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C183" s="16" t="n">
-        <f aca="false">ROUNDUP(C182*Paramètres!$B$17,0)</f>
+        <f aca="false">MAX(1,ROUNDUP(C181/Paramètres!$B$16,0))</f>
+        <v>5</v>
+      </c>
+      <c r="D183" s="16" t="n">
+        <f aca="false">MAX(1,ROUNDUP(D181/Paramètres!$B$16,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <f aca="false">MAX(1,ROUNDUP(E181/Paramètres!$B$16,0))</f>
+        <v>1</v>
+      </c>
+      <c r="F183" s="2"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C184" s="16" t="n">
+        <f aca="false">ROUNDUP(C183*Paramètres!$B$17,0)</f>
         <v>8</v>
       </c>
-      <c r="D183" s="16" t="n">
-        <f aca="false">ROUNDUP(D182*Paramètres!$B$17,0)</f>
+      <c r="D184" s="16" t="n">
+        <f aca="false">ROUNDUP(D183*Paramètres!$B$17,0)</f>
         <v>10</v>
       </c>
-      <c r="E183" s="16" t="n">
-        <f aca="false">ROUNDUP(E182*Paramètres!$B$17,0)</f>
+      <c r="E184" s="16" t="n">
+        <f aca="false">ROUNDUP(E183*Paramètres!$B$17,0)</f>
         <v>2</v>
       </c>
-      <c r="F183" s="2"/>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
+      <c r="F184" s="2"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="B186" s="11"/>
-      <c r="C186" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F186" s="2"/>
+      <c r="A186" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B187" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C187" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D187" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E187" s="15" t="n">
-        <v>0</v>
+        <v>325</v>
+      </c>
+      <c r="B187" s="11"/>
+      <c r="C187" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E187" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="F187" s="2"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C188" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D188" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E188" s="15" t="n">
         <v>0</v>
@@ -7039,86 +7089,86 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B189" s="11"/>
-      <c r="C189" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E189" s="13" t="s">
-        <v>60</v>
+        <v>329</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C189" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="B190" s="11" t="s">
-        <v>328</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="B190" s="11"/>
       <c r="C190" s="12" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="E190" s="13" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="F190" s="2"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="C191" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" s="15" t="n">
-        <v>0</v>
+        <v>333</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E191" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="F191" s="2"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="C192" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>173</v>
+        <v>335</v>
+      </c>
+      <c r="C192" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F192" s="2"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>173</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>173</v>
+        <v>326</v>
       </c>
       <c r="E193" s="13" t="s">
         <v>173</v>
@@ -7127,171 +7177,189 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="C194" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E194" s="15" t="n">
-        <v>0</v>
+        <v>339</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="F194" s="2"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B195" s="11"/>
-      <c r="C195" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D195" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E195" s="13" t="s">
-        <v>173</v>
+        <v>340</v>
+      </c>
+      <c r="B195" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C195" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F195" s="2"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C196" s="18" t="n">
+        <v>342</v>
+      </c>
+      <c r="B196" s="11"/>
+      <c r="C196" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E196" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F196" s="2"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C197" s="18" t="n">
         <f aca="false">IF(C109="Oui",Abonnements!$D$10,0)+IF(C88="Oui",Abonnements!$D$9,IF(C7="Aucun",0,IF(C23&gt;10,Abonnements!$D$7,Abonnements!$D$6)))+IF(OR(C7="Immersif",C11&gt;0),Abonnements!$D$8,0)</f>
         <v>20</v>
       </c>
-      <c r="D196" s="18" t="n">
+      <c r="D197" s="18" t="n">
         <f aca="false">IF(D109="Oui",Abonnements!$D$10,0)+IF(D88="Oui",Abonnements!$D$9,IF(D7="Aucun",0,IF(D23&gt;10,Abonnements!$D$7,Abonnements!$D$6)))+IF(OR(D7="Immersif",D11&gt;0),Abonnements!$D$8,0)</f>
         <v>15</v>
       </c>
-      <c r="E196" s="18" t="n">
+      <c r="E197" s="18" t="n">
         <f aca="false">IF(E109="Oui",Abonnements!$D$10,0)+IF(E88="Oui",Abonnements!$D$9,IF(E7="Aucun",0,IF(E23&gt;10,Abonnements!$D$7,Abonnements!$D$6)))+IF(OR(E7="Immersif",E11&gt;0),Abonnements!$D$8,0)</f>
         <v>10</v>
       </c>
-      <c r="F196" s="2"/>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="C197" s="18" t="n">
-        <f aca="false">IF(C7="Aucun",0,Abonnements!$D$12+C23*Abonnements!$D$13+C12*Abonnements!$D$14)+IF(C88="Oui",Abonnements!$D$15,0)+IF(C109="Oui",Abonnements!$D$16+C145*Abonnements!$D$17,0)</f>
-        <v>30</v>
-      </c>
-      <c r="D197" s="18" t="n">
-        <f aca="false">IF(D7="Aucun",0,Abonnements!$D$12+D23*Abonnements!$D$13+D12*Abonnements!$D$14)+IF(D88="Oui",Abonnements!$D$15,0)+IF(D109="Oui",Abonnements!$D$16+D145*Abonnements!$D$17,0)</f>
-        <v>33</v>
-      </c>
-      <c r="E197" s="18" t="n">
-        <f aca="false">IF(E7="Aucun",0,Abonnements!$D$12+E23*Abonnements!$D$13+E12*Abonnements!$D$14)+IF(E88="Oui",Abonnements!$D$15,0)+IF(E109="Oui",Abonnements!$D$16+E145*Abonnements!$D$17,0)</f>
-        <v>15.5</v>
-      </c>
       <c r="F197" s="2"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C198" s="18" t="n">
-        <f aca="false">C187*Abonnements!$D$19+C188*Abonnements!$D$20+IF(C189="Local",Abonnements!$D$21,IF(C189="Régional",Abonnements!$D$22,IF(C189="National",Abonnements!$D$23,0)))+IF(C190="Oui",Abonnements!$D$24,0)+C191*Abonnements!$D$25+IF(C192="Oui",Abonnements!$D$26,0)+IF(C193="Oui",Abonnements!$D$27,0)+C194*Abonnements!$D$28</f>
+        <f aca="false">IF(C7="Aucun",0,Abonnements!$D$12+C23*Abonnements!$D$13+C12*Abonnements!$D$14)+IF(C88="Oui",Abonnements!$D$15,0)+IF(C109="Oui",Abonnements!$D$16+C150*Abonnements!$D$17,0)</f>
+        <v>30</v>
+      </c>
+      <c r="D198" s="18" t="n">
+        <f aca="false">IF(D7="Aucun",0,Abonnements!$D$12+D23*Abonnements!$D$13+D12*Abonnements!$D$14)+IF(D88="Oui",Abonnements!$D$15,0)+IF(D109="Oui",Abonnements!$D$16+D150*Abonnements!$D$17,0)</f>
+        <v>33</v>
+      </c>
+      <c r="E198" s="18" t="n">
+        <f aca="false">IF(E7="Aucun",0,Abonnements!$D$12+E23*Abonnements!$D$13+E12*Abonnements!$D$14)+IF(E88="Oui",Abonnements!$D$15,0)+IF(E109="Oui",Abonnements!$D$16+E150*Abonnements!$D$17,0)</f>
+        <v>15.5</v>
+      </c>
+      <c r="F198" s="2"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C199" s="18" t="n">
+        <f aca="false">C188*Abonnements!$D$19+C189*Abonnements!$D$20+IF(C190="Local",Abonnements!$D$21,IF(C190="Régional",Abonnements!$D$22,IF(C190="National",Abonnements!$D$23,0)))+IF(C191="Oui",Abonnements!$D$24,0)+C192*Abonnements!$D$25+IF(C193="Oui",Abonnements!$D$26,0)+IF(C194="Oui",Abonnements!$D$27,0)+C195*Abonnements!$D$28</f>
         <v>40</v>
       </c>
-      <c r="D198" s="18" t="n">
-        <f aca="false">D187*Abonnements!$D$19+D188*Abonnements!$D$20+IF(D189="Local",Abonnements!$D$21,IF(D189="Régional",Abonnements!$D$22,IF(D189="National",Abonnements!$D$23,0)))+IF(D190="Oui",Abonnements!$D$24,0)+D191*Abonnements!$D$25+IF(D192="Oui",Abonnements!$D$26,0)+IF(D193="Oui",Abonnements!$D$27,0)+D194*Abonnements!$D$28</f>
+      <c r="D199" s="18" t="n">
+        <f aca="false">D188*Abonnements!$D$19+D189*Abonnements!$D$20+IF(D190="Local",Abonnements!$D$21,IF(D190="Régional",Abonnements!$D$22,IF(D190="National",Abonnements!$D$23,0)))+IF(D191="Oui",Abonnements!$D$24,0)+D192*Abonnements!$D$25+IF(D193="Oui",Abonnements!$D$26,0)+IF(D194="Oui",Abonnements!$D$27,0)+D195*Abonnements!$D$28</f>
         <v>125</v>
       </c>
-      <c r="E198" s="18" t="n">
-        <f aca="false">E187*Abonnements!$D$19+E188*Abonnements!$D$20+IF(E189="Local",Abonnements!$D$21,IF(E189="Régional",Abonnements!$D$22,IF(E189="National",Abonnements!$D$23,0)))+IF(E190="Oui",Abonnements!$D$24,0)+E191*Abonnements!$D$25+IF(E192="Oui",Abonnements!$D$26,0)+IF(E193="Oui",Abonnements!$D$27,0)+E194*Abonnements!$D$28</f>
-        <v>0</v>
-      </c>
-      <c r="F198" s="2"/>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="C199" s="24" t="n">
-        <f aca="false">IF(C186="Oui",ROUND((C196+C197+C198)*Paramètres!$B$6*IF(C195="Oui",1-Abonnements!$D$30,1),0),0)</f>
+      <c r="E199" s="18" t="n">
+        <f aca="false">E188*Abonnements!$D$19+E189*Abonnements!$D$20+IF(E190="Local",Abonnements!$D$21,IF(E190="Régional",Abonnements!$D$22,IF(E190="National",Abonnements!$D$23,0)))+IF(E191="Oui",Abonnements!$D$24,0)+E192*Abonnements!$D$25+IF(E193="Oui",Abonnements!$D$26,0)+IF(E194="Oui",Abonnements!$D$27,0)+E195*Abonnements!$D$28</f>
+        <v>0</v>
+      </c>
+      <c r="F199" s="2"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C200" s="24" t="n">
+        <f aca="false">IF(C187="Oui",ROUND((C197+C198+C199)*Paramètres!$B$6*IF(C196="Oui",1-Abonnements!$D$30,1),0),0)</f>
         <v>90</v>
       </c>
-      <c r="D199" s="24" t="n">
-        <f aca="false">IF(D186="Oui",ROUND((D196+D197+D198)*Paramètres!$B$6*IF(D195="Oui",1-Abonnements!$D$30,1),0),0)</f>
+      <c r="D200" s="24" t="n">
+        <f aca="false">IF(D187="Oui",ROUND((D197+D198+D199)*Paramètres!$B$6*IF(D196="Oui",1-Abonnements!$D$30,1),0),0)</f>
         <v>173</v>
       </c>
-      <c r="E199" s="24" t="n">
-        <f aca="false">IF(E186="Oui",ROUND((E196+E197+E198)*Paramètres!$B$6*IF(E195="Oui",1-Abonnements!$D$30,1),0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9"/>
+      <c r="E200" s="24" t="n">
+        <f aca="false">IF(E187="Oui",ROUND((E197+E198+E199)*Paramètres!$B$6*IF(E196="Oui",1-Abonnements!$D$30,1),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B202" s="11"/>
-      <c r="C202" s="29" t="n">
-        <v>1247</v>
-      </c>
-      <c r="D202" s="29" t="n">
-        <v>3174</v>
-      </c>
-      <c r="E202" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F202" s="2"/>
+      <c r="A202" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="C203" s="17" t="n">
-        <f aca="false">IF(C202&gt;0,C171/C202-1,0)</f>
-        <v>2.24779470729751</v>
-      </c>
-      <c r="D203" s="17" t="n">
-        <f aca="false">IF(D202&gt;0,D171/D202-1,0)</f>
-        <v>0.30119722747322</v>
-      </c>
-      <c r="E203" s="17" t="n">
-        <f aca="false">IF(E202&gt;0,E171/E202-1,0)</f>
+        <v>349</v>
+      </c>
+      <c r="B203" s="11"/>
+      <c r="C203" s="29" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D203" s="29" t="n">
+        <v>3174</v>
+      </c>
+      <c r="E203" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F203" s="2"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B204" s="11"/>
-      <c r="C204" s="29" t="n">
+        <v>350</v>
+      </c>
+      <c r="C204" s="17" t="n">
+        <f aca="false">IF(C203&gt;0,C174/C203-1,0)</f>
+        <v>2.24779470729751</v>
+      </c>
+      <c r="D204" s="17" t="n">
+        <f aca="false">IF(D203&gt;0,D174/D203-1,0)</f>
+        <v>0.30119722747322</v>
+      </c>
+      <c r="E204" s="17" t="n">
+        <f aca="false">IF(E203&gt;0,E174/E203-1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F204" s="2"/>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B205" s="11"/>
+      <c r="C205" s="29" t="n">
         <v>85</v>
       </c>
-      <c r="D204" s="29" t="n">
+      <c r="D205" s="29" t="n">
         <v>162</v>
       </c>
-      <c r="E204" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" s="2"/>
+      <c r="E205" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -7303,11 +7371,11 @@
       <formula1>Référencement!$A$6:$A$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C88:E88 C90:E90 C109:E109 C161:E162 C165:E165 C186:E186 C190:E190 C192:E193 C195:E195" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C88:E88 C90:E90 C109:E109 C168:E168 C187:E187 C191:E191 C193:E194 C196:E196" type="list">
       <formula1>"Oui,Non"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C189:E189" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C190:E190" type="list">
       <formula1>"Aucun,Local,Régional,National"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7342,61 +7410,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B5" s="32" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B7" s="34" t="n">
         <v>0.9</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B8" s="34" t="n">
         <v>1.15</v>
@@ -7405,29 +7473,29 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B9" s="32" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B10" s="35" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B11" s="35" t="n">
         <v>30</v>
@@ -7436,73 +7504,73 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B12" s="34" t="n">
         <v>0.6</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B13" s="34" t="n">
         <v>0.4</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B14" s="34" t="n">
         <v>0.4</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B15" s="34" t="n">
         <v>0.2</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B16" s="36" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B17" s="37" t="n">
         <v>1.6</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B18" s="32" t="n">
         <v>3000</v>
@@ -7511,7 +7579,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B19" s="35" t="n">
         <v>5</v>
@@ -7549,12 +7617,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7565,27 +7633,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7597,13 +7665,13 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>0</v>
@@ -7616,21 +7684,21 @@
         <v>0</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D7" s="38" t="n">
         <v>15</v>
@@ -7643,21 +7711,21 @@
         <v>2.5</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>30</v>
@@ -7670,15 +7738,15 @@
         <v>20</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -7690,13 +7758,13 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>0</v>
@@ -7709,21 +7777,21 @@
         <v/>
       </c>
       <c r="G10" s="31" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D11" s="38" t="n">
         <v>40</v>
@@ -7736,19 +7804,19 @@
         <v>40</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D12" s="38" t="n">
         <v>0</v>
@@ -7761,21 +7829,21 @@
         <v/>
       </c>
       <c r="G12" s="31" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D13" s="38" t="n">
         <v>0</v>
@@ -7788,19 +7856,19 @@
         <v/>
       </c>
       <c r="G13" s="31" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D14" s="41" t="n">
         <v>0.5</v>
@@ -7813,7 +7881,7 @@
         <v/>
       </c>
       <c r="G14" s="31" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H14" s="31"/>
     </row>
@@ -7847,17 +7915,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -7870,26 +7938,26 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -7898,7 +7966,7 @@
         <v>60</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="38" t="n">
@@ -7920,7 +7988,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="38" t="n">
@@ -7936,15 +8004,15 @@
         <v>1</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C8" s="31"/>
       <c r="D8" s="38" t="n">
@@ -7960,7 +8028,7 @@
         <v>1.25</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7968,7 +8036,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="38" t="n">
@@ -7984,7 +8052,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7992,7 +8060,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="38" t="n">
@@ -8008,7 +8076,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8019,27 +8087,27 @@
         <v>28</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -8051,13 +8119,13 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D14" s="38" t="n">
         <v>300</v>
@@ -8070,10 +8138,10 @@
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8081,10 +8149,10 @@
         <v>46</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>20</v>
@@ -8097,13 +8165,13 @@
         <v>50</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H15" s="31"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -8115,13 +8183,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D17" s="38" t="n">
         <v>0</v>
@@ -8134,10 +8202,10 @@
         <v/>
       </c>
       <c r="G17" s="31" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8148,7 +8216,7 @@
         <v>68</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D18" s="38" t="n">
         <v>120</v>
@@ -8161,7 +8229,7 @@
         <v>48</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H18" s="31"/>
     </row>
@@ -8173,7 +8241,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D19" s="38" t="n">
         <v>250</v>
@@ -8186,7 +8254,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="H19" s="31"/>
     </row>
@@ -8198,7 +8266,7 @@
         <v>72</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D20" s="38" t="n">
         <v>90</v>
@@ -8211,7 +8279,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H20" s="31"/>
     </row>
@@ -8223,7 +8291,7 @@
         <v>74</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>600</v>
@@ -8236,7 +8304,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H21" s="31"/>
     </row>
@@ -8248,7 +8316,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D22" s="38" t="n">
         <v>200</v>
@@ -8261,7 +8329,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H22" s="31"/>
     </row>
@@ -8273,7 +8341,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D23" s="38" t="n">
         <v>120</v>
@@ -8286,7 +8354,7 @@
         <v>48</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H23" s="31"/>
     </row>
@@ -8298,7 +8366,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D24" s="38" t="n">
         <v>80</v>
@@ -8311,7 +8379,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H24" s="31"/>
     </row>
@@ -8323,7 +8391,7 @@
         <v>82</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D25" s="38" t="n">
         <v>90</v>
@@ -8336,7 +8404,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H25" s="31"/>
     </row>
@@ -8348,7 +8416,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D26" s="38" t="n">
         <v>90</v>
@@ -8361,7 +8429,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H26" s="31"/>
     </row>
@@ -8373,7 +8441,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D27" s="38" t="n">
         <v>90</v>
@@ -8386,7 +8454,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H27" s="31"/>
     </row>
@@ -8398,7 +8466,7 @@
         <v>88</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D28" s="38" t="n">
         <v>900</v>
@@ -8411,7 +8479,7 @@
         <v>50</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H28" s="31"/>
     </row>
@@ -8423,7 +8491,7 @@
         <v>90</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D29" s="38" t="n">
         <v>200</v>
@@ -8436,10 +8504,10 @@
         <v>50</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8450,7 +8518,7 @@
         <v>92</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D30" s="38" t="n">
         <v>350</v>
@@ -8463,7 +8531,7 @@
         <v>50</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H30" s="31"/>
     </row>
@@ -8475,7 +8543,7 @@
         <v>94</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D31" s="38" t="n">
         <v>90</v>
@@ -8488,7 +8556,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H31" s="31"/>
     </row>
@@ -8500,7 +8568,7 @@
         <v>96</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D32" s="38" t="n">
         <v>30</v>
@@ -8513,7 +8581,7 @@
         <v>60</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H32" s="31"/>
     </row>
@@ -8525,7 +8593,7 @@
         <v>98</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D33" s="38" t="n">
         <v>450</v>
@@ -8538,7 +8606,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="H33" s="31"/>
     </row>
@@ -8550,7 +8618,7 @@
         <v>100</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D34" s="38" t="n">
         <v>150</v>
@@ -8563,7 +8631,7 @@
         <v>50</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H34" s="31"/>
     </row>
@@ -8575,7 +8643,7 @@
         <v>102</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D35" s="38" t="n">
         <v>60</v>
@@ -8588,7 +8656,7 @@
         <v>48</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H35" s="31"/>
     </row>
@@ -8600,7 +8668,7 @@
         <v>104</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D36" s="38" t="n">
         <v>80</v>
@@ -8613,13 +8681,13 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H36" s="31"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -8637,7 +8705,7 @@
         <v>108</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D38" s="38" t="n">
         <v>700</v>
@@ -8650,10 +8718,10 @@
         <v>50</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8664,7 +8732,7 @@
         <v>110</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D39" s="38" t="n">
         <v>250</v>
@@ -8677,7 +8745,7 @@
         <v>50</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H39" s="31"/>
     </row>
@@ -8689,7 +8757,7 @@
         <v>112</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D40" s="38" t="n">
         <v>180</v>
@@ -8702,7 +8770,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H40" s="31"/>
     </row>
@@ -8714,7 +8782,7 @@
         <v>114</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D41" s="38" t="n">
         <v>220</v>
@@ -8727,7 +8795,7 @@
         <v>48.8888888888889</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="H41" s="31"/>
     </row>
@@ -8739,7 +8807,7 @@
         <v>116</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D42" s="38" t="n">
         <v>90</v>
@@ -8752,7 +8820,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="H42" s="31"/>
     </row>
@@ -8764,7 +8832,7 @@
         <v>118</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D43" s="38" t="n">
         <v>80</v>
@@ -8777,7 +8845,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="H43" s="31"/>
     </row>
@@ -8789,7 +8857,7 @@
         <v>120</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D44" s="38" t="n">
         <v>70</v>
@@ -8802,7 +8870,7 @@
         <v>46.6666666666667</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="H44" s="31"/>
     </row>
@@ -8814,7 +8882,7 @@
         <v>122</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D45" s="38" t="n">
         <v>150</v>
@@ -8827,7 +8895,7 @@
         <v>50</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H45" s="31"/>
     </row>
@@ -8839,7 +8907,7 @@
         <v>124</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D46" s="38" t="n">
         <v>120</v>
@@ -8852,7 +8920,7 @@
         <v>48</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H46" s="31"/>
     </row>
@@ -8864,7 +8932,7 @@
         <v>126</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D47" s="38" t="n">
         <v>150</v>
@@ -8877,13 +8945,13 @@
         <v>50</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H47" s="31"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -8901,7 +8969,7 @@
         <v>130</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D49" s="38" t="n">
         <v>60</v>
@@ -8914,7 +8982,7 @@
         <v>48</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H49" s="31"/>
     </row>
@@ -8926,7 +8994,7 @@
         <v>132</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D50" s="38" t="n">
         <v>60</v>
@@ -8939,7 +9007,7 @@
         <v>48</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="H50" s="31"/>
     </row>
@@ -8951,7 +9019,7 @@
         <v>134</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D51" s="38" t="n">
         <v>20</v>
@@ -8964,7 +9032,7 @@
         <v>50</v>
       </c>
       <c r="G51" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H51" s="31"/>
     </row>
@@ -8987,7 +9055,7 @@
         <v>50</v>
       </c>
       <c r="G52" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H52" s="31"/>
     </row>
@@ -8999,7 +9067,7 @@
         <v>138</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D53" s="38" t="n">
         <v>10</v>
@@ -9012,7 +9080,7 @@
         <v>50</v>
       </c>
       <c r="G53" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H53" s="31"/>
     </row>
@@ -9024,7 +9092,7 @@
         <v>140</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D54" s="38" t="n">
         <v>40</v>
@@ -9037,7 +9105,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G54" s="31" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="H54" s="31"/>
     </row>
@@ -9075,17 +9143,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -9099,34 +9167,34 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9134,10 +9202,10 @@
         <v>60</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>0</v>
@@ -9158,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9166,10 +9234,10 @@
         <v>58</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D7" s="38" t="n">
         <v>150</v>
@@ -9190,7 +9258,7 @@
         <v>0.05</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9198,10 +9266,10 @@
         <v>59</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>350</v>
@@ -9222,18 +9290,18 @@
         <v>0.12</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>650</v>
@@ -9254,18 +9322,18 @@
         <v>0.2</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>1200</v>
@@ -9286,12 +9354,12 @@
         <v>0.3</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -9305,30 +9373,30 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,7 +9404,7 @@
         <v>63</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="38" t="n">
@@ -9354,18 +9422,18 @@
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>150</v>
@@ -9387,13 +9455,13 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>400</v>
@@ -9410,12 +9478,12 @@
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
       <c r="J16" s="31" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -9435,22 +9503,22 @@
         <v>28</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9461,7 +9529,7 @@
         <v>144</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D20" s="38" t="n">
         <v>150</v>
@@ -9474,7 +9542,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H20" s="31"/>
     </row>
@@ -9486,7 +9554,7 @@
         <v>146</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>200</v>
@@ -9499,10 +9567,10 @@
         <v>50</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9513,7 +9581,7 @@
         <v>148</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D22" s="38" t="n">
         <v>90</v>
@@ -9526,7 +9594,7 @@
         <v>51.4285714285714</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H22" s="31"/>
     </row>
@@ -9538,7 +9606,7 @@
         <v>150</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D23" s="38" t="n">
         <v>45</v>
@@ -9551,7 +9619,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H23" s="31"/>
     </row>
@@ -9563,7 +9631,7 @@
         <v>152</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D24" s="38" t="n">
         <v>120</v>
@@ -9576,7 +9644,7 @@
         <v>48</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H24" s="31"/>
     </row>
@@ -9588,7 +9656,7 @@
         <v>154</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D25" s="38" t="n">
         <v>150</v>
@@ -9601,7 +9669,7 @@
         <v>50</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H25" s="31"/>
     </row>
@@ -9613,7 +9681,7 @@
         <v>156</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D26" s="38" t="n">
         <v>40</v>
@@ -9626,7 +9694,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H26" s="31"/>
     </row>
@@ -9638,7 +9706,7 @@
         <v>158</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D27" s="38" t="n">
         <v>120</v>
@@ -9651,7 +9719,7 @@
         <v>48</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="H27" s="31"/>
     </row>
@@ -9663,7 +9731,7 @@
         <v>160</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D28" s="38" t="n">
         <v>80</v>
@@ -9676,7 +9744,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="H28" s="31"/>
     </row>
@@ -9688,7 +9756,7 @@
         <v>162</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D29" s="38" t="n">
         <v>60</v>
@@ -9701,7 +9769,7 @@
         <v>48</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H29" s="31"/>
     </row>
@@ -9713,7 +9781,7 @@
         <v>164</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D30" s="38" t="n">
         <v>4</v>
@@ -9726,7 +9794,7 @@
         <v>50</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H30" s="31"/>
     </row>
@@ -9749,7 +9817,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H31" s="31"/>
     </row>
@@ -9761,7 +9829,7 @@
         <v>168</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D32" s="38" t="n">
         <v>200</v>
@@ -9774,13 +9842,13 @@
         <v>50</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H32" s="31"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="42" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -9794,7 +9862,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="43" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B36" s="43"/>
       <c r="C36" s="43"/>
@@ -9845,7 +9913,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9856,27 +9924,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -9888,13 +9956,13 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>1100</v>
@@ -9907,13 +9975,13 @@
         <v>55</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -9925,13 +9993,13 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>3</v>
@@ -9944,21 +10012,21 @@
         <v>50</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>120</v>
@@ -9971,21 +10039,21 @@
         <v>48</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D10" s="41" t="n">
         <v>0.5</v>
@@ -9998,21 +10066,21 @@
         <v>50</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D11" s="38" t="n">
         <v>15</v>
@@ -10025,13 +10093,13 @@
         <v>50</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="H11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -10049,7 +10117,7 @@
         <v>183</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D13" s="38" t="n">
         <v>150</v>
@@ -10062,7 +10130,7 @@
         <v>50</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H13" s="31"/>
     </row>
@@ -10074,7 +10142,7 @@
         <v>185</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D14" s="38" t="n">
         <v>200</v>
@@ -10087,7 +10155,7 @@
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H14" s="31"/>
     </row>
@@ -10099,7 +10167,7 @@
         <v>187</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>400</v>
@@ -10112,7 +10180,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H15" s="31"/>
     </row>
@@ -10124,7 +10192,7 @@
         <v>189</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>150</v>
@@ -10137,7 +10205,7 @@
         <v>50</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H16" s="31"/>
     </row>
@@ -10149,7 +10217,7 @@
         <v>191</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D17" s="38" t="n">
         <v>300</v>
@@ -10162,7 +10230,7 @@
         <v>50</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H17" s="31"/>
     </row>
@@ -10174,7 +10242,7 @@
         <v>193</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D18" s="38" t="n">
         <v>450</v>
@@ -10187,10 +10255,10 @@
         <v>50</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10212,7 +10280,7 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H19" s="31"/>
     </row>
@@ -10235,7 +10303,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H20" s="31"/>
     </row>
@@ -10247,7 +10315,7 @@
         <v>199</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>150</v>
@@ -10260,7 +10328,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H21" s="31"/>
     </row>
@@ -10283,7 +10351,7 @@
         <v>48</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H22" s="31"/>
     </row>
@@ -10304,7 +10372,7 @@
     <tabColor rgb="FFF69106"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -10317,12 +10385,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10333,27 +10401,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -10365,13 +10433,13 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>900</v>
@@ -10384,15 +10452,15 @@
         <v>50</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -10410,7 +10478,7 @@
         <v>209</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>350</v>
@@ -10423,7 +10491,7 @@
         <v>50</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H8" s="31"/>
     </row>
@@ -10435,7 +10503,7 @@
         <v>211</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>400</v>
@@ -10448,7 +10516,7 @@
         <v>50</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H9" s="31"/>
     </row>
@@ -10460,7 +10528,7 @@
         <v>213</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>450</v>
@@ -10473,10 +10541,10 @@
         <v>50</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10487,7 +10555,7 @@
         <v>215</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D11" s="38" t="n">
         <v>250</v>
@@ -10500,7 +10568,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H11" s="31"/>
     </row>
@@ -10523,7 +10591,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H12" s="31"/>
     </row>
@@ -10535,7 +10603,7 @@
         <v>219</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D13" s="38" t="n">
         <v>200</v>
@@ -10548,13 +10616,13 @@
         <v>50</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -10572,7 +10640,7 @@
         <v>221</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>450</v>
@@ -10585,7 +10653,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H15" s="31"/>
     </row>
@@ -10597,7 +10665,7 @@
         <v>223</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>400</v>
@@ -10610,7 +10678,7 @@
         <v>50</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H16" s="31"/>
     </row>
@@ -10622,7 +10690,7 @@
         <v>225</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D17" s="38" t="n">
         <v>500</v>
@@ -10635,7 +10703,7 @@
         <v>50</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H17" s="31"/>
     </row>
@@ -10647,7 +10715,7 @@
         <v>227</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D18" s="38" t="n">
         <v>500</v>
@@ -10660,7 +10728,7 @@
         <v>50</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H18" s="31"/>
     </row>
@@ -10683,7 +10751,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H19" s="31"/>
     </row>
@@ -10695,7 +10763,7 @@
         <v>231</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D20" s="38" t="n">
         <v>350</v>
@@ -10708,7 +10776,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H20" s="31"/>
     </row>
@@ -10731,7 +10799,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H21" s="31"/>
     </row>
@@ -10743,7 +10811,7 @@
         <v>235</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D22" s="38" t="n">
         <v>300</v>
@@ -10756,13 +10824,13 @@
         <v>50</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H22" s="31"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -10791,10 +10859,10 @@
         <v>50</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10805,7 +10873,7 @@
         <v>239</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D25" s="38" t="n">
         <v>450</v>
@@ -10818,7 +10886,7 @@
         <v>50</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H25" s="31"/>
     </row>
@@ -10841,7 +10909,7 @@
         <v>50</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H26" s="31"/>
     </row>
@@ -10853,7 +10921,7 @@
         <v>243</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D27" s="38" t="n">
         <v>300</v>
@@ -10866,7 +10934,7 @@
         <v>50</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H27" s="31"/>
     </row>
@@ -10889,10 +10957,10 @@
         <v>50</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10903,7 +10971,7 @@
         <v>247</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D29" s="38" t="n">
         <v>600</v>
@@ -10916,13 +10984,13 @@
         <v>50</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -10940,7 +11008,7 @@
         <v>249</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D31" s="38" t="n">
         <v>500</v>
@@ -10953,7 +11021,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H31" s="31"/>
     </row>
@@ -10965,7 +11033,7 @@
         <v>251</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D32" s="38" t="n">
         <v>450</v>
@@ -10978,7 +11046,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H32" s="31"/>
     </row>
@@ -11001,7 +11069,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H33" s="31"/>
     </row>
@@ -11013,7 +11081,7 @@
         <v>255</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D34" s="38" t="n">
         <v>400</v>
@@ -11026,7 +11094,7 @@
         <v>50</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H34" s="31"/>
     </row>
@@ -11038,7 +11106,7 @@
         <v>257</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D35" s="38" t="n">
         <v>400</v>
@@ -11051,13 +11119,13 @@
         <v>50</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H35" s="31"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -11075,7 +11143,7 @@
         <v>259</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D37" s="38" t="n">
         <v>350</v>
@@ -11088,7 +11156,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H37" s="31"/>
     </row>
@@ -11111,7 +11179,7 @@
         <v>50</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H38" s="31"/>
     </row>
@@ -11123,7 +11191,7 @@
         <v>263</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D39" s="38" t="n">
         <v>250</v>
@@ -11136,7 +11204,7 @@
         <v>50</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H39" s="31"/>
     </row>
@@ -11159,7 +11227,7 @@
         <v>50</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H40" s="31"/>
     </row>
@@ -11171,7 +11239,7 @@
         <v>267</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D41" s="38" t="n">
         <v>250</v>
@@ -11184,13 +11252,13 @@
         <v>50</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="H41" s="31"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -11202,284 +11270,429 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D43" s="38" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E43" s="39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F43" s="40" t="n">
         <f aca="false">IF(E43&gt;0,D43/E43,"")</f>
         <v>50</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="H43" s="31"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D44" s="38" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E44" s="39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44" s="40" t="n">
         <f aca="false">IF(E44&gt;0,D44/E44,"")</f>
         <v>50</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="H44" s="31"/>
+        <v>607</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D45" s="38" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E45" s="39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F45" s="40" t="n">
         <f aca="false">IF(E45&gt;0,D45/E45,"")</f>
         <v>50</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="H45" s="31"/>
+        <v>607</v>
+      </c>
+      <c r="H45" s="31" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="D46" s="38" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E46" s="39" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F46" s="40" t="n">
         <f aca="false">IF(E46&gt;0,D46/E46,"")</f>
         <v>50</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="H46" s="31" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>643</v>
+      </c>
+      <c r="H46" s="31"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="D47" s="38" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="39" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F47" s="40" t="n">
         <f aca="false">IF(E47&gt;0,D47/E47,"")</f>
         <v>50</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>636</v>
-      </c>
-      <c r="H47" s="31"/>
+        <v>607</v>
+      </c>
+      <c r="H47" s="31" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B49" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="C48" s="31" t="s">
-        <v>637</v>
-      </c>
-      <c r="D48" s="38" t="n">
+      <c r="C49" s="31" t="s">
+        <v>646</v>
+      </c>
+      <c r="D49" s="38" t="n">
         <v>250</v>
       </c>
-      <c r="E48" s="39" t="n">
+      <c r="E49" s="39" t="n">
         <v>5</v>
-      </c>
-      <c r="F48" s="40" t="n">
-        <f aca="false">IF(E48&gt;0,D48/E48,"")</f>
-        <v>50</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="H48" s="31"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>638</v>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>300</v>
-      </c>
-      <c r="E49" s="39" t="n">
-        <v>6</v>
       </c>
       <c r="F49" s="40" t="n">
         <f aca="false">IF(E49&gt;0,D49/E49,"")</f>
         <v>50</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>639</v>
+        <v>393</v>
       </c>
       <c r="H49" s="31"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C50" s="31"/>
+        <v>285</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>647</v>
+      </c>
       <c r="D50" s="38" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E50" s="39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="40" t="n">
         <f aca="false">IF(E50&gt;0,D50/E50,"")</f>
         <v>50</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H50" s="31"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="31" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="D51" s="38" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E51" s="39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="40" t="n">
         <f aca="false">IF(E51&gt;0,D51/E51,"")</f>
         <v>50</v>
       </c>
       <c r="G51" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H51" s="31"/>
     </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>649</v>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>600</v>
+      </c>
+      <c r="E52" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" s="40" t="n">
+        <f aca="false">IF(E52&gt;0,D52/E52,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H52" s="31" t="s">
+        <v>650</v>
+      </c>
+    </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
+      <c r="A53" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>651</v>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="E53" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="40" t="n">
+        <f aca="false">IF(E53&gt;0,D53/E53,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>652</v>
+      </c>
+      <c r="H53" s="31"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>250</v>
+      </c>
+      <c r="E54" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="40" t="n">
+        <f aca="false">IF(E54&gt;0,D54/E54,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H54" s="31"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="44" t="n">
+      <c r="A55" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>654</v>
+      </c>
+      <c r="D55" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="E55" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" s="40" t="n">
+        <f aca="false">IF(E55&gt;0,D55/E55,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G55" s="31" t="s">
+        <v>655</v>
+      </c>
+      <c r="H55" s="31"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="C56" s="31"/>
+      <c r="D56" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="E56" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" s="40" t="n">
+        <f aca="false">IF(E56&gt;0,D56/E56,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G56" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H56" s="31"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>656</v>
+      </c>
+      <c r="D57" s="38" t="n">
+        <v>200</v>
+      </c>
+      <c r="E57" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="40" t="n">
+        <f aca="false">IF(E57&gt;0,D57/E57,"")</f>
+        <v>50</v>
+      </c>
+      <c r="G57" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H57" s="31"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+    </row>
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="B55" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="44" t="n">
+      <c r="B61" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="21" t="n">
+      <c r="B62" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="44" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="44" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="21" t="n">
+      <c r="B63" s="21" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="44" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="44" t="n">
         <v>31</v>
       </c>
-      <c r="B58" s="21" t="n">
+      <c r="B64" s="21" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -11513,12 +11726,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11529,27 +11742,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -11561,13 +11774,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>10</v>
@@ -11580,16 +11793,16 @@
         <v/>
       </c>
       <c r="G6" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="38" t="n">
@@ -11603,19 +11816,19 @@
         <v/>
       </c>
       <c r="G7" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="D8" s="38" t="n">
         <v>5</v>
@@ -11628,16 +11841,16 @@
         <v/>
       </c>
       <c r="G8" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="38" t="n">
@@ -11651,19 +11864,19 @@
         <v/>
       </c>
       <c r="G9" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>30</v>
@@ -11676,13 +11889,13 @@
         <v/>
       </c>
       <c r="G10" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -11694,13 +11907,13 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="D12" s="38" t="n">
         <v>15</v>
@@ -11713,16 +11926,16 @@
         <v>60</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="41" t="n">
@@ -11736,16 +11949,16 @@
         <v>50</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="H13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="41" t="n">
@@ -11759,19 +11972,19 @@
         <v/>
       </c>
       <c r="G14" s="31" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="H14" s="31"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>15</v>
@@ -11784,16 +11997,16 @@
         <v>60</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H15" s="31"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="38" t="n">
@@ -11807,16 +12020,16 @@
         <v>50</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="38" t="n">
@@ -11830,13 +12043,13 @@
         <v>50</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="H17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -11848,13 +12061,13 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D19" s="38" t="n">
         <v>10</v>
@@ -11867,13 +12080,13 @@
         <v>50</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="H19" s="31"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>132</v>
@@ -11890,19 +12103,19 @@
         <v>50</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="H20" s="31"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D21" s="38" t="n">
         <v>60</v>
@@ -11915,19 +12128,19 @@
         <v>48</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H21" s="31"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="D22" s="38" t="n">
         <v>120</v>
@@ -11940,19 +12153,19 @@
         <v>48</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H22" s="31"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="D23" s="38" t="n">
         <v>220</v>
@@ -11965,19 +12178,19 @@
         <v>48.8888888888889</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="D24" s="38" t="n">
         <v>40</v>
@@ -11990,19 +12203,19 @@
         <v>50</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="D25" s="38" t="n">
         <v>80</v>
@@ -12015,19 +12228,19 @@
         <v>53.3333333333333</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="H25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="D26" s="38" t="n">
         <v>25</v>
@@ -12040,19 +12253,19 @@
         <v>50</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="D27" s="38" t="n">
         <v>15</v>
@@ -12065,21 +12278,21 @@
         <v>50</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="D28" s="38" t="n">
         <v>35</v>
@@ -12092,15 +12305,15 @@
         <v>35</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -12112,10 +12325,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="34" t="n">
@@ -12129,10 +12342,10 @@
         <v/>
       </c>
       <c r="G30" s="31" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
